--- a/reproducibility_artifact/code/app/research/cross_edition/annotation_packets/h3prime_tennessee_2022_2024/Annotator_G_ANNOTATION.xlsx
+++ b/reproducibility_artifact/code/app/research/cross_edition/annotation_packets/h3prime_tennessee_2022_2024/Annotator_G_ANNOTATION.xlsx
@@ -1,201 +1,186 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME FIRST" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tennessee 2022-23 -&gt; Sept2024 (" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tennessee 2022-23 -&gt; Sept2024 ('!$A$1:$I$93</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME FIRST" sheetId="1" r:id="Rc88b6dd43e544a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tennessee 2022-23 -&gt; Sept2024 (" sheetId="2" r:id="R9036d806c2434eb3"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-  </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="7">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF595959"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="2">
+    <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="8">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+  <x:colors>
+    <x:indexedColors>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00000000"/>
+      <x:rgbColor rgb="00FFFFFF"/>
+      <x:rgbColor rgb="00FF0000"/>
+      <x:rgbColor rgb="0000FF00"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008000"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00808000"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="00C0C0C0"/>
+      <x:rgbColor rgb="00808080"/>
+      <x:rgbColor rgb="009999FF"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00FFFFCC"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00660066"/>
+      <x:rgbColor rgb="00FF8080"/>
+      <x:rgbColor rgb="000066CC"/>
+      <x:rgbColor rgb="00CCCCFF"/>
+      <x:rgbColor rgb="00000080"/>
+      <x:rgbColor rgb="00FF00FF"/>
+      <x:rgbColor rgb="00FFFF00"/>
+      <x:rgbColor rgb="0000FFFF"/>
+      <x:rgbColor rgb="00800080"/>
+      <x:rgbColor rgb="00800000"/>
+      <x:rgbColor rgb="00008080"/>
+      <x:rgbColor rgb="000000FF"/>
+      <x:rgbColor rgb="0000CCFF"/>
+      <x:rgbColor rgb="00CCFFFF"/>
+      <x:rgbColor rgb="00CCFFCC"/>
+      <x:rgbColor rgb="00FFFF99"/>
+      <x:rgbColor rgb="0099CCFF"/>
+      <x:rgbColor rgb="00FF99CC"/>
+      <x:rgbColor rgb="00CC99FF"/>
+      <x:rgbColor rgb="00FFCC99"/>
+      <x:rgbColor rgb="003366FF"/>
+      <x:rgbColor rgb="0033CCCC"/>
+      <x:rgbColor rgb="0099CC00"/>
+      <x:rgbColor rgb="00FFCC00"/>
+      <x:rgbColor rgb="00FF9900"/>
+      <x:rgbColor rgb="00FF6600"/>
+      <x:rgbColor rgb="00666699"/>
+      <x:rgbColor rgb="00969696"/>
+      <x:rgbColor rgb="00003366"/>
+      <x:rgbColor rgb="00339966"/>
+      <x:rgbColor rgb="00003300"/>
+      <x:rgbColor rgb="00333300"/>
+      <x:rgbColor rgb="00993300"/>
+      <x:rgbColor rgb="00993366"/>
+      <x:rgbColor rgb="00333399"/>
+      <x:rgbColor rgb="00333333"/>
+    </x:indexedColors>
+  </x:colors>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -241,72 +226,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -362,7 +289,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -371,13 +298,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -411,17 +338,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -476,264 +392,252 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Annotation task - Annotator G</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>What you're doing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>You're checking whether specific safety recommendations from an older edition of an EMS (emergency medical) protocol document still exist in a newer edition - and if so, whether they changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>This is NOT a medical judgement. It's a matching task: 'is this the same instruction, somewhere in the new document - reworded or not - or was it removed?'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Where to work</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>This workbook has one tab per document pair (see tabs at the bottom). Each tab has 60 rows to judge. Work through all rows on all tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>What to read, per row</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Column E (yellow header) - the OLD recommendation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Column F - the FULL new edition guideline it might now belong to. Read through it and look for the same instruction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>What to fill in (yellow cells, columns G-I)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Column G - type the matching item's ID exactly as it appears at the start of that item in column F, OR type NONE if you're confident it was removed, OR type CANNOT_DETERMINE if you truly can't tell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Column H - pick one from the dropdown: unchanged / reworded / substantive / merged / split / moved. (Leave blank if you answered NONE.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Column I - optional. Explain anything unsure, especially CANNOT_DETERMINE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>1. Work alone. Don't discuss rows with the other annotator, or compare answers, until you have BOTH finished every tab. This is the whole point - we're measuring how often two people agree without coordinating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2. Don't guess if you're not sure - CANNOT_DETERMINE is a normal, expected answer sometimes, not a failure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>3. You do not need any other file. Everything you need is in column F.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>When you're done</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Save this file and send it back exactly as-is (don't rename tabs or columns). That's it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Tabs (bottom of screen): each is one document pair, 60 rows each.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="100" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Annotation task - Annotator G</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">What you're doing</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">You're checking whether specific safety recommendations from an older edition of an EMS (emergency medical) protocol document still exist in a newer edition - and if so, whether they changed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This is NOT a medical judgement. It's a matching task: 'is this the same instruction, somewhere in the new document - reworded or not - or was it removed?'</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Where to work</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This workbook has one tab per document pair (see tabs at the bottom). Each tab has 60 rows to judge. Work through all rows on all tabs.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">What to read, per row</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32" customHeight="1">
+      <x:c r="A9" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Column E (yellow header) - the OLD recommendation.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32" customHeight="1">
+      <x:c r="A10" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Column F - the FULL new edition guideline it might now belong to. Read through it and look for the same instruction.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">What to fill in (yellow cells, columns G-I)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32" customHeight="1">
+      <x:c r="A12" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Column G - type the matching item's ID exactly as it appears at the start of that item in column F, OR type NONE if you're confident it was removed, OR type CANNOT_DETERMINE if you truly can't tell.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Column H - pick one from the dropdown: unchanged / reworded / substantive / merged / split / moved. (Leave blank if you answered NONE.)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="32" customHeight="1">
+      <x:c r="A14" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Column I - optional. Explain anything unsure, especially CANNOT_DETERMINE.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rules</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. Work alone. Don't discuss rows with the other annotator, or compare answers, until you have BOTH finished every tab. This is the whole point - we're measuring how often two people agree without coordinating.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2. Don't guess if you're not sure - CANNOT_DETERMINE is a normal, expected answer sometimes, not a failure.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3. You do not need any other file. Everything you need is in column F.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">When you're done</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Save this file and send it back exactly as-is (don't rename tabs or columns). That's it.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tabs (bottom of screen): each is one document pair, 60 rows each.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>sample_id</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>old_item_id</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>old_guideline</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>old_section</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>OLD RECOMMENDATION (read this)</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>NEW EDITION - everything in the matching guideline (search this for a match)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER: matching new item ID, or NONE, or CANNOT_DETERMINE</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER: relation</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>YOUR NOTES (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>hypothermia/notes/o</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Hypothermia</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>[hypothermia/notes/o]
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" customWidth="1"/>
+    <x:col min="2" max="2" width="26" customWidth="1"/>
+    <x:col min="3" max="3" width="22" customWidth="1"/>
+    <x:col min="4" max="4" width="16" customWidth="1"/>
+    <x:col min="5" max="5" width="46" customWidth="1"/>
+    <x:col min="6" max="6" width="60" customWidth="1"/>
+    <x:col min="7" max="7" width="30" customWidth="1"/>
+    <x:col min="8" max="8" width="16" customWidth="1"/>
+    <x:col min="9" max="9" width="30" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sample_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">old_item_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">old_guideline</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">old_section</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OLD RECOMMENDATION (read this)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NEW EDITION - everything in the matching guideline (search this for a match)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">YOUR ANSWER: matching new item ID, or NONE, or CANNOT_DETERMINE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">YOUR ANSWER: relation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">YOUR NOTES (optional)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="60" customHeight="1">
+      <x:c r="A2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypothermia/notes/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypothermia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hypothermia/notes/o]
 Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:
 [hypothermia/notes/o#2]
 Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:
@@ -778,42 +682,46 @@
 [hypothermia/emt stop here/15.b]
 Withhold medications and further shocks until patient warmed to &gt;85°F
 [hypothermia/emt stop here/15.c]
-Continue CPR and rewarming attempts</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr"/>
-      <c r="H2" s="7" t="inlineStr"/>
-      <c r="I2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>hypothermia/notes/o#2</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Hypothermia</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>[hypothermia/notes/o]
+Continue CPR and rewarming attempts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>hypothermia/notes/o</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str"/>
+    </x:row>
+    <x:row r="3" ht="60" customHeight="1">
+      <x:c r="A3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypothermia/notes/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypothermia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hypothermia/notes/o]
 Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:
 [hypothermia/notes/o#2]
 Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:
@@ -858,42 +766,46 @@
 [hypothermia/emt stop here/15.b]
 Withhold medications and further shocks until patient warmed to &gt;85°F
 [hypothermia/emt stop here/15.c]
-Continue CPR and rewarming attempts</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="7" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>hypothermia/notes/o#3</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Hypothermia</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>95°F – amnesia, poor judgment, hyperventilation, bradycardia, shivering</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>[hypothermia/notes/o]
+Continue CPR and rewarming attempts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="7" t="str">
+        <x:v>hypothermia/notes/o#2</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str"/>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypothermia/notes/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypothermia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">95°F – amnesia, poor judgment, hyperventilation, bradycardia, shivering</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hypothermia/notes/o]
 Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:
 [hypothermia/notes/o#2]
 Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:
@@ -938,42 +850,46 @@
 [hypothermia/emt stop here/15.b]
 Withhold medications and further shocks until patient warmed to &gt;85°F
 [hypothermia/emt stop here/15.c]
-Continue CPR and rewarming attempts</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr"/>
-      <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>hypothermia/notes/o#4</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Hypothermia</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>90°F – loss of coordination (drunken appearance), decreasing rate and depth of respirations, shivering ceases or bradycardia</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>[hypothermia/notes/o]
+Continue CPR and rewarming attempts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>hypothermia/notes/o#3</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str"/>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypothermia/notes/o#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypothermia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">90°F – loss of coordination (drunken appearance), decreasing rate and depth of respirations, shivering ceases or bradycardia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hypothermia/notes/o]
 Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:
 [hypothermia/notes/o#2]
 Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:
@@ -1018,42 +934,46 @@
 [hypothermia/emt stop here/15.b]
 Withhold medications and further shocks until patient warmed to &gt;85°F
 [hypothermia/emt stop here/15.c]
-Continue CPR and rewarming attempts</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>hypothermia/notes/o#5</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Hypothermia</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>85°F – decreased LOC, slow respirations, atrial fibrillation, decreased BP, decreased heart rate, ventricular irritability</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>[hypothermia/notes/o]
+Continue CPR and rewarming attempts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="7" t="str">
+        <x:v>hypothermia/notes/o#4</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="str"/>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypothermia/notes/o#5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypothermia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">85°F – decreased LOC, slow respirations, atrial fibrillation, decreased BP, decreased heart rate, ventricular irritability</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hypothermia/notes/o]
 Heat packs or warm water bottles to the groin, axillary, and cervical areas If patient is unresponsive, rewarm passively:
 [hypothermia/notes/o#2]
 Increase the room temperature gradually, cover with blankets The following signs and symptoms are found at varying body core temperature:
@@ -1098,162 +1018,178 @@
 [hypothermia/emt stop here/15.b]
 Withhold medications and further shocks until patient warmed to &gt;85°F
 [hypothermia/emt stop here/15.c]
-Continue CPR and rewarming attempts</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>S006</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest blunt/treatment pathway/o</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Blunt)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Apnea</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest blunt/treatment pathway/o]
+Continue CPR and rewarming attempts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
+        <x:v>hypothermia/notes/o#5</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="str"/>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest blunt/treatment pathway/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Blunt)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Apnea</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest blunt/treatment pathway/o]
 Apnea
 [adult trauma arrest blunt/treatment pathway/o#2]
 Pulselessness
 [adult trauma arrest blunt/treatment pathway/o#3]
-Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>S007</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest blunt/treatment pathway/o#2</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Blunt)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Pulselessness</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest blunt/treatment pathway/o]
+Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="7" t="str">
+        <x:v>adult trauma arrest blunt/treatment pathway/o</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="str"/>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest blunt/treatment pathway/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Blunt)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pulselessness</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest blunt/treatment pathway/o]
 Apnea
 [adult trauma arrest blunt/treatment pathway/o#2]
 Pulselessness
 [adult trauma arrest blunt/treatment pathway/o#3]
-Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>S008</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest blunt/treatment pathway/o#3</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Blunt)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest blunt/treatment pathway/o]
+Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="7" t="str">
+        <x:v>adult trauma arrest blunt/treatment pathway/o#2</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str"/>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest blunt/treatment pathway/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Blunt)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest blunt/treatment pathway/o]
 Apnea
 [adult trauma arrest blunt/treatment pathway/o#2]
 Pulselessness
 [adult trauma arrest blunt/treatment pathway/o#3]
-Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>S009</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest penetrating/treatment pathway/o</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Penetrating)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Apnea</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest penetrating/treatment pathway/o]
+Asystole or PEA &lt;40 If patient does not meet all the above criteria, Initiate resuscitation per protocol. Consider chest decompression in these patients prior to discontinuing resuscitative efforts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="7" t="str">
+        <x:v>adult trauma arrest blunt/treatment pathway/o#3</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="str"/>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest penetrating/treatment pathway/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Penetrating)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Apnea</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest penetrating/treatment pathway/o]
 Apnea
 [adult trauma arrest penetrating/treatment pathway/o#2]
 Pulselessness
@@ -1262,42 +1198,46 @@
 [adult trauma arrest penetrating/treatment pathway/o#4]
 Absence of Pupillary Reflexes
 [adult trauma arrest penetrating/treatment pathway/o#5]
-No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>S010</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest penetrating/treatment pathway/o#2</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Penetrating)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Pulselessness</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest penetrating/treatment pathway/o]
+No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="7" t="str">
+        <x:v>adult trauma arrest penetrating/treatment pathway/o</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="str"/>
+    </x:row>
+    <x:row r="11" ht="60" customHeight="1">
+      <x:c r="A11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest penetrating/treatment pathway/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Penetrating)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pulselessness</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest penetrating/treatment pathway/o]
 Apnea
 [adult trauma arrest penetrating/treatment pathway/o#2]
 Pulselessness
@@ -1306,42 +1246,46 @@
 [adult trauma arrest penetrating/treatment pathway/o#4]
 Absence of Pupillary Reflexes
 [adult trauma arrest penetrating/treatment pathway/o#5]
-No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest penetrating/treatment pathway/o#3</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Penetrating)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Asystole or PEA &lt;40</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest penetrating/treatment pathway/o]
+No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="7" t="str">
+        <x:v>adult trauma arrest penetrating/treatment pathway/o#2</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="str"/>
+    </x:row>
+    <x:row r="12" ht="60" customHeight="1">
+      <x:c r="A12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest penetrating/treatment pathway/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Penetrating)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Asystole or PEA &lt;40</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest penetrating/treatment pathway/o]
 Apnea
 [adult trauma arrest penetrating/treatment pathway/o#2]
 Pulselessness
@@ -1350,42 +1294,46 @@
 [adult trauma arrest penetrating/treatment pathway/o#4]
 Absence of Pupillary Reflexes
 [adult trauma arrest penetrating/treatment pathway/o#5]
-No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>S012</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest penetrating/treatment pathway/o#4</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Penetrating)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Absence of Pupillary Reflexes</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest penetrating/treatment pathway/o]
+No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>adult trauma arrest penetrating/treatment pathway/o#3</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="str"/>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
+      <x:c r="A13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S012</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest penetrating/treatment pathway/o#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Penetrating)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Absence of Pupillary Reflexes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest penetrating/treatment pathway/o]
 Apnea
 [adult trauma arrest penetrating/treatment pathway/o#2]
 Pulselessness
@@ -1394,42 +1342,46 @@
 [adult trauma arrest penetrating/treatment pathway/o#4]
 Absence of Pupillary Reflexes
 [adult trauma arrest penetrating/treatment pathway/o#5]
-No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>S013</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>adult trauma arrest penetrating/treatment pathway/o#5</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Adult Trauma Arrest (Penetrating)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>[adult trauma arrest penetrating/treatment pathway/o]
+No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>adult trauma arrest penetrating/treatment pathway/o#4</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="str"/>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
+      <x:c r="A14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adult trauma arrest penetrating/treatment pathway/o#5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Adult Trauma Arrest (Penetrating)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[adult trauma arrest penetrating/treatment pathway/o]
 Apnea
 [adult trauma arrest penetrating/treatment pathway/o#2]
 Pulselessness
@@ -1438,42 +1390,46 @@
 [adult trauma arrest penetrating/treatment pathway/o#4]
 Absence of Pupillary Reflexes
 [adult trauma arrest penetrating/treatment pathway/o#5]
-No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>S014</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/miscellaneous/1.o</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>miscellaneous</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>All males &gt; 40 years old</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+No Spontaneous movements If patient does not meet all the above criteria, Initiate resuscitation per protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>adult trauma arrest penetrating/treatment pathway/o#5</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="str"/>
+    </x:row>
+    <x:row r="15" ht="60" customHeight="1">
+      <x:c r="A15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/miscellaneous/1.o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">miscellaneous</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All males &gt; 40 years old</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -1738,42 +1694,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>S015</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/miscellaneous/1.o#2</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>miscellaneous</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>All females &gt; 50 years old Nausea and vomiting</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/miscellaneous/1.o</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="str"/>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
+      <x:c r="A16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S015</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/miscellaneous/1.o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">miscellaneous</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All females &gt; 50 years old Nausea and vomiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -2038,42 +1998,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/miscellaneous/1.o#3</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>miscellaneous</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>All males &gt; 40 years old</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/miscellaneous/1.o#2</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="str"/>
+    </x:row>
+    <x:row r="17" ht="60" customHeight="1">
+      <x:c r="A17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S016</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/miscellaneous/1.o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">miscellaneous</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All males &gt; 40 years old</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -2338,42 +2302,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>S017</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/miscellaneous/1.o#4</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>miscellaneous</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>All females &gt; 50 years old Shortness of breath – all new onset All diabetics and smokers whose symptoms may be cardiac related Known heart disease (including CHF, post-surgery, previous MI) Weakness – new onset Syncope Unresponsive Patients with sympathomimetically active drug use (cocaine, crack, methamphetamine, etc.)</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/miscellaneous/1.o#3</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I17" s="7" t="str"/>
+    </x:row>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/miscellaneous/1.o#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">miscellaneous</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All females &gt; 50 years old Shortness of breath – all new onset All diabetics and smokers whose symptoms may be cardiac related Known heart disease (including CHF, post-surgery, previous MI) Weakness – new onset Syncope Unresponsive Patients with sympathomimetically active drug use (cocaine, crack, methamphetamine, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -2638,42 +2606,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>S018</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/treatment and interventions/11.o</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>treatment and interventions</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Consider use of padded pediatric motion restricting board</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/miscellaneous/1.o#4</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I18" s="7" t="str"/>
+    </x:row>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S018</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/treatment and interventions/11.o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment and interventions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consider use of padded pediatric motion restricting board</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -2938,42 +2910,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>S019</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/treatment and interventions/11.o#2</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>treatment and interventions</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Avoid methods that provoke increased spinal movement</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/treatment and interventions/11.o</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I19" s="7" t="str"/>
+    </x:row>
+    <x:row r="20" ht="60" customHeight="1">
+      <x:c r="A20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S019</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/treatment and interventions/11.o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment and interventions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Avoid methods that provoke increased spinal movement</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -3238,42 +3214,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>S020</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/treatment and interventions/11.o#3</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>treatment and interventions</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>If choosing to apply SMR to patient in car seat, ensure that proper assessment of patient posterior is performed Combative patients: Avoid methods that provoke increased spinal movement and/or combativeness. Pediatric Patients and Car Seats Infants restrained in a rear-facing car seat and children restrained in a car seat (with a high back – convertible or booster) may receive SMR and be extricated in the car seat, the child may remain in the seat if the SMR is secure and his/her condition allows (no signs of respiratory distress or shock). Children restrained in booster seat (without a back) need to be extricated and receive standard SMR procedures. Helmet Removal Safe and proper removal of the helmet should be done following the steps outlined in an approved trauma curriculum. Indications for football helmet removal: When a patient is wearing a helmet and not shoulder pads In the presence of head and/or facial trauma, and removal of the face piece is not sufficient Patients requiring advanced airway management when removal of the facemask is not sufficient When the helmet is loose on the patient’s head BLS/ALS State of Tennessee Protocol Guidelines 2022-23 In the presence of cardiopulmonary arrest (the shoulder pads must also be removed) When helmet and shoulder pads are both on the spine is kept in neutral alignment. If the patient is wearing only a helmet or shoulder pads, neutral alignment must be maintained. Either remove the other piece of equipment or pad under the missing piece. All other helmets must be removed in order to maintain spinal alignment. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/treatment and interventions/11.o#2</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="str"/>
+    </x:row>
+    <x:row r="21" ht="60" customHeight="1">
+      <x:c r="A21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/treatment and interventions/11.o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment and interventions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If choosing to apply SMR to patient in car seat, ensure that proper assessment of patient posterior is performed Combative patients: Avoid methods that provoke increased spinal movement and/or combativeness. Pediatric Patients and Car Seats Infants restrained in a rear-facing car seat and children restrained in a car seat (with a high back – convertible or booster) may receive SMR and be extricated in the car seat, the child may remain in the seat if the SMR is secure and his/her condition allows (no signs of respiratory distress or shock). Children restrained in booster seat (without a back) need to be extricated and receive standard SMR procedures. Helmet Removal Safe and proper removal of the helmet should be done following the steps outlined in an approved trauma curriculum. Indications for football helmet removal: When a patient is wearing a helmet and not shoulder pads In the presence of head and/or facial trauma, and removal of the face piece is not sufficient Patients requiring advanced airway management when removal of the facemask is not sufficient When the helmet is loose on the patient’s head BLS/ALS State of Tennessee Protocol Guidelines 2022-23 In the presence of cardiopulmonary arrest (the shoulder pads must also be removed) When helmet and shoulder pads are both on the spine is kept in neutral alignment. If the patient is wearing only a helmet or shoulder pads, neutral alignment must be maintained. Either remove the other piece of equipment or pad under the missing piece. All other helmets must be removed in order to maintain spinal alignment. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -3538,42 +3518,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>S021</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/contraindications/o</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>contraindications</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>If the device has been accidentally closed, push the side buttons inward with one hand and pull the device open using the device arms. Locate wound edges. Align the device parallel to the length of the wound edge. Position the needles approx. 1-2 cm from the wound edge on either side. For very large wounds the device can be applied to one side, then pulled to the other side, or the tissue can be approximated by hand and the device applied. Press the arms of the device together to close the device. The device’s safety seal will break with pressure. Ensure the entire wound is sealed and bleeding stops, using a gauze pad to wipe the area to verify no leaking of blood from the wound. More than one device may be required for large wounds. If bleeding continues:</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/treatment and interventions/11.o#3</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I21" s="7" t="str"/>
+    </x:row>
+    <x:row r="22" ht="60" customHeight="1">
+      <x:c r="A22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S021</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/contraindications/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">contraindications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If the device has been accidentally closed, push the side buttons inward with one hand and pull the device open using the device arms. Locate wound edges. Align the device parallel to the length of the wound edge. Position the needles approx. 1-2 cm from the wound edge on either side. For very large wounds the device can be applied to one side, then pulled to the other side, or the tissue can be approximated by hand and the device applied. Press the arms of the device together to close the device. The device’s safety seal will break with pressure. Ensure the entire wound is sealed and bleeding stops, using a gauze pad to wipe the area to verify no leaking of blood from the wound. More than one device may be required for large wounds. If bleeding continues:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -4089,42 +4073,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>S022</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/contraindications/o#2</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>contraindications</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Ensure the device is in the correct position, close the device more firmly by applying further pressure to the arms of the device.</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="str"/>
+      <x:c r="I22" s="7" t="str"/>
+    </x:row>
+    <x:row r="23" ht="60" customHeight="1">
+      <x:c r="A23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S022</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/contraindications/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">contraindications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ensure the device is in the correct position, close the device more firmly by applying further pressure to the arms of the device.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -4640,42 +4626,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>S023</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/contraindications/o#3</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>contraindications</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>If wound is too large, apply additional devices to the open section.</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="str"/>
+      <x:c r="I23" s="7" t="str"/>
+    </x:row>
+    <x:row r="24" ht="60" customHeight="1">
+      <x:c r="A24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/contraindications/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">contraindications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If wound is too large, apply additional devices to the open section.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -5191,42 +5179,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>S024</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/contraindications/o#4</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>contraindications</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>If device is applied incorrectly or not positioned properly, remove the device according to the instructions and reapply. Consider Pain Management protocol</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="str"/>
+      <x:c r="I24" s="7" t="str"/>
+    </x:row>
+    <x:row r="25" ht="60" customHeight="1">
+      <x:c r="A25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/contraindications/o#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">contraindications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If device is applied incorrectly or not positioned properly, remove the device according to the instructions and reapply. Consider Pain Management protocol</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -5742,42 +5732,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>S025</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/indications/o</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>indications</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Presence of indwelling port</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="str"/>
+      <x:c r="I25" s="7" t="str"/>
+    </x:row>
+    <x:row r="26" ht="60" customHeight="1">
+      <x:c r="A26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/indications/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">indications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Presence of indwelling port</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -6293,42 +6285,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>S026</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/indications/o#2</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>indications</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Altered mental status (GCS of 8 or less)</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="str"/>
+      <x:c r="I26" s="7" t="str"/>
+    </x:row>
+    <x:row r="27" ht="60" customHeight="1">
+      <x:c r="A27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S026</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/indications/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">indications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Altered mental status (GCS of 8 or less)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -6844,42 +6838,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>S027</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/indications/o#3</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>indications</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Respiratory compromise (SaO2 of 80% or less following appropriate oxygen therapy, and/or respiratory rate &lt; 10 or &gt; 40 /min.) Hemodynamically unstable</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="str"/>
+      <x:c r="I27" s="7" t="str"/>
+    </x:row>
+    <x:row r="28" ht="60" customHeight="1">
+      <x:c r="A28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S027</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/indications/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">indications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Respiratory compromise (SaO2 of 80% or less following appropriate oxygen therapy, and/or respiratory rate &lt; 10 or &gt; 40 /min.) Hemodynamically unstable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -7395,42 +7391,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>S028</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/notes/o</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Consider rotating the foot to the mid-line position (foot straight up and down)</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="str"/>
+      <x:c r="I28" s="7" t="str"/>
+    </x:row>
+    <x:row r="29" ht="60" customHeight="1">
+      <x:c r="A29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S028</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/notes/o</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consider rotating the foot to the mid-line position (foot straight up and down)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -7946,42 +7944,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>S029</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/notes/o#2</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>With the knee slightly flexed, lift the foot off of the surface allowing the lower leg to “hang” dependent</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="str"/>
+      <x:c r="I29" s="7" t="str"/>
+    </x:row>
+    <x:row r="30" ht="60" customHeight="1">
+      <x:c r="A30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S029</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/notes/o#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">With the knee slightly flexed, lift the foot off of the surface allowing the lower leg to “hang” dependent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -8497,42 +8497,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>S030</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/notes/o#3</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>This maneuver may improve your ability to visualize and access the tibial insertion site</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="str"/>
+      <x:c r="I30" s="7" t="str"/>
+    </x:row>
+    <x:row r="31" ht="60" customHeight="1">
+      <x:c r="A31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S030</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/notes/o#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This maneuver may improve your ability to visualize and access the tibial insertion site</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -9048,42 +9050,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>S031</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/notes/o#4</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Please use the Bariatric Needle Set in these patients Landmarks: Humeral Head Place the patient in a supine position. Expose the shoulder and place the patient’s arm against the patient’s body. Rest the elbow on the stretcher with the forearm on the abdomen. Palpate and identify the mid shaft humerus and continue palpating toward the humeral head. As you near the shoulder you will note a small protrusion. This is the base of the greater tubercle insertion site. With the opposite hand “pinch” the anterior and inferior aspects of the humeral head confirming the identification of the greater tubercle. This will ensure you have identified the midline of the humerus itself. The insertion site is approximately two finger widths inferior to the coracoid process and the acromion. Landmarks: Medial Malleolus The insertion site is two finger widths proximal to the Medial Malleolus and positioned midline on the medial shaft. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="str"/>
+      <x:c r="I31" s="7" t="str"/>
+    </x:row>
+    <x:row r="32" ht="60" customHeight="1">
+      <x:c r="A32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S031</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/notes/o#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Please use the Bariatric Needle Set in these patients Landmarks: Humeral Head Place the patient in a supine position. Expose the shoulder and place the patient’s arm against the patient’s body. Rest the elbow on the stretcher with the forearm on the abdomen. Palpate and identify the mid shaft humerus and continue palpating toward the humeral head. As you near the shoulder you will note a small protrusion. This is the base of the greater tubercle insertion site. With the opposite hand “pinch” the anterior and inferior aspects of the humeral head confirming the identification of the greater tubercle. This will ensure you have identified the midline of the humerus itself. The insertion site is approximately two finger widths inferior to the coracoid process and the acromion. Landmarks: Medial Malleolus The insertion site is two finger widths proximal to the Medial Malleolus and positioned midline on the medial shaft. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -9599,42 +9603,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>S032</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>post-intubation sedation/paramedic/-</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Post-Intubation Sedation</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>paramedic</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>[post-intubation sedation/paramedic only/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str"/>
+      <x:c r="I32" s="7" t="str"/>
+    </x:row>
+    <x:row r="33" ht="60" customHeight="1">
+      <x:c r="A33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S032</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post-intubation sedation/paramedic/-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post-Intubation Sedation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">paramedic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post-intubation sedation/paramedic only/1]
 An infant is less than one year of age.
 [post-intubation sedation/paramedic only/2]
 A child is from one to eight years of age.
@@ -9653,42 +9659,46 @@
 [post-intubation sedation/paramedic only/9]
 Children may be effectively ventilated using a BVM. This is the preferred method of ventilation in respiratory or cardiac arrest. EMT AEMT
 [post-intubation sedation/paramedic/-]
-1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>S033</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>trauma - penetrating/aemt stop here/9</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Trauma - Penetrating</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>aemt stop here</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Contact Medical Control for pain management authorization.</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>[trauma - penetrating/notes/1]
+1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>post-intubation sedation/paramedic/-</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str"/>
+    </x:row>
+    <x:row r="34" ht="60" customHeight="1">
+      <x:c r="A34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S033</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">trauma - penetrating/aemt stop here/9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Trauma - Penetrating</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aemt stop here</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Contact Medical Control for pain management authorization.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[trauma - penetrating/notes/1]
 Initiate in-line C-Spine protection while simultaneously evaluating and controlling the patient’s ABCs. Incorporate the mechanism of injury into the patient care scheme.
 [trauma - penetrating/notes/2]
 Control any hemorrhage and simultaneously provide oxygen and airway maintenance appropriate to patient’s condition.
@@ -9711,42 +9721,46 @@
 [trauma - penetrating/aemt stop here/3]
 Label syringe Adult Push Dose Pressor IV Administration: Using above EPINEPHrine preparation (EPINEPHrine 10mcg/ml) 10 ml syringe, administer 5-10 mcg (0.5-1 ml) slow IV push (over 30-60 seconds) every 2-5 minutes as needed as a temporizing measure for severe hypotension. Note: Monitor HR and BP continuously while administering/titrating EPINEPHrine, as it may cause significant tachycardia and tachyarrhythmia in addition to the desired vasoconstriction
 [trauma - penetrating/aemt stop here/9]
-Contact Medical Control for pain management authorization.</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>S034</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>post resuscitation/emt stop here/13</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Post Resuscitation</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>emt stop here</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Ensure Head of Bed elevated 30°.</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>[post resuscitation/notes/1]
+Contact Medical Control for pain management authorization.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>trauma - penetrating/aemt stop here/9</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str"/>
+    </x:row>
+    <x:row r="35" ht="60" customHeight="1">
+      <x:c r="A35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S034</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post resuscitation/emt stop here/13</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">emt stop here</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ensure Head of Bed elevated 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post resuscitation/notes/1]
 Oxygen and airway maintenance appropriate for patient’s condition.
 [post resuscitation/notes/2]
 Supportive care.
@@ -9783,42 +9797,46 @@
 [post resuscitation/emt stop here/12]
 Initiate Induced Hypothermia protocol if appropriate.
 [post resuscitation/emt stop here/13]
-Ensure Head of Bed elevated 30°.</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>S035</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/7#5</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Withdraw the Bougie only to a depth sufficient to allow loading of the ET tube while maintaining proximal control of the Bougie.</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Ensure Head of Bed elevated 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>post resuscitation/emt stop here/13</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="str"/>
+    </x:row>
+    <x:row r="36" ht="60" customHeight="1">
+      <x:c r="A36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S035</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/7#5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Withdraw the Bougie only to a depth sufficient to allow loading of the ET tube while maintaining proximal control of the Bougie.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -10334,42 +10352,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>S036</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>neonatal resuscitation/treatment pathway/6</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Neonatal Resuscitation</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Pulse oximetry.</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>[neonatal resuscitation/treatment pathway/8]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H36" s="7" t="str"/>
+      <x:c r="I36" s="7" t="str"/>
+    </x:row>
+    <x:row r="37" ht="60" customHeight="1">
+      <x:c r="A37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S036</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">neonatal resuscitation/treatment pathway/6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Neonatal Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pulse oximetry.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[neonatal resuscitation/treatment pathway/8]
 INT or IV NS, if hypotensive bolus 20 cc/kg.
 [neonatal resuscitation/treatment pathway/9]
 If pulse rate is &gt; 60 keep warm, ventilate with BVM if necessary, transport.
@@ -10410,42 +10430,46 @@
 [neonatal resuscitation/treatment pathway/6]
 Pulse oximetry.
 [neonatal resuscitation/treatment pathway/7]
-Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>S037</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>non-formulary medications/treatment pathway/6</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Non-Formulary Medications</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>If the medication(s) is not administered the documentation must include those reasons for withholding.</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>[non-formulary medications/treatment pathway/3]
+Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>neonatal resuscitation/treatment pathway/6</x:v>
+      </x:c>
+      <x:c r="H37" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I37" s="7" t="str"/>
+    </x:row>
+    <x:row r="38" ht="60" customHeight="1">
+      <x:c r="A38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S037</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">non-formulary medications/treatment pathway/6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Non-Formulary Medications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If the medication(s) is not administered the documentation must include those reasons for withholding.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[non-formulary medications/treatment pathway/3]
 Necessary medication(s) administration as requested by caregiver(s):
 [non-formulary medications/treatment pathway/3.a]
 Caregiver must provide the medication(s) to be administered
@@ -10484,42 +10508,46 @@
 [non-formulary medications/treatment pathway/1]
 Oxygen and airway maintenance appropriate to the patient’s condition.
 [non-formulary medications/treatment pathway/2]
-Other treatments will be in accordance with the BLS / ALS SOPs.</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>S038</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>medications at schools/treatment pathway/3.c.v</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Medications at Schools</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Name of the medication(s)</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>[medications at schools/treatment pathway/3]
+Other treatments will be in accordance with the BLS / ALS SOPs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>non-formulary medications/treatment pathway/6</x:v>
+      </x:c>
+      <x:c r="H38" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I38" s="7" t="str"/>
+    </x:row>
+    <x:row r="39" ht="60" customHeight="1">
+      <x:c r="A39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S038</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">medications at schools/treatment pathway/3.c.v</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medications at Schools</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Name of the medication(s)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[medications at schools/treatment pathway/3]
 Necessary medication(s) administration as requested by caregiver(s):
 [medications at schools/treatment pathway/3.a]
 Schools must provide the medication(s) to be administered
@@ -10558,42 +10586,46 @@
 [medications at schools/treatment pathway/1]
 Oxygen and airway maintenance appropriate for the patient’s condition.
 [medications at schools/treatment pathway/2]
-Other treatments will be in accordance with the BLS / ALS SOPs.</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>S039</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/6#2</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Document that blood was delivered and obtain replacement blood draw kit from vending machine prior to return to service.</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Other treatments will be in accordance with the BLS / ALS SOPs.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="7" t="str">
+        <x:v>medications at schools/treatment pathway/3.c.v</x:v>
+      </x:c>
+      <x:c r="H39" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I39" s="7" t="str"/>
+    </x:row>
+    <x:row r="40" ht="60" customHeight="1">
+      <x:c r="A40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S039</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/6#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document that blood was delivered and obtain replacement blood draw kit from vending machine prior to return to service.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -11109,42 +11141,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>S040</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/paramedic only/3#4</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>paramedic only</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Cyanotic, cold (Arsenic)</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H40" s="7" t="str"/>
+      <x:c r="I40" s="7" t="str"/>
+    </x:row>
+    <x:row r="41" ht="60" customHeight="1">
+      <x:c r="A41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S040</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/paramedic only/3#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">paramedic only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cyanotic, cold (Arsenic)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -11660,42 +11694,46 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>S041</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/2#11</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Using ResQPOD on an Endotracheal Tube or I-Gel:</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>delirium with hyperagitation/paramedic only/3#4</x:v>
+      </x:c>
+      <x:c r="H41" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I41" s="7" t="str"/>
+    </x:row>
+    <x:row r="42" ht="60" customHeight="1">
+      <x:c r="A42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S041</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/2#11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Using ResQPOD on an Endotracheal Tube or I-Gel:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -12211,42 +12249,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>S042</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>neurogenic shock/treatment pathway/1</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Neurogenic Shock</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Draw up 9 ml of normal saline into 10 ml syringe</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>[neurogenic shock/treatment pathway/8]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H42" s="7" t="str"/>
+      <x:c r="I42" s="7" t="str"/>
+    </x:row>
+    <x:row r="43" ht="60" customHeight="1">
+      <x:c r="A43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S042</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">neurogenic shock/treatment pathway/1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Neurogenic Shock</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Draw up 9 ml of normal saline into 10 ml syringe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[neurogenic shock/treatment pathway/8]
 If refractory hypotension: EPINEPHrine 2-10 mcg/min (peds 0.1-1 mcg/kg/min). To prepare EPINEPHrine 10 mcg/ml:
 [neurogenic shock/treatment pathway/1]
 Draw up 9 ml of normal saline into 10 ml syringe
@@ -12267,42 +12307,46 @@
 [neurogenic shock/treatment pathway/5]
 Hemorrhage control - Consider tourniquet use or hemorrhage control clamp.
 [neurogenic shock/treatment pathway/6]
-Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>S043</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/12#3</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Consider ketamine if sedation is necessary during high quality CPR. NOTE: Placement and initiation of the device cannot exceed 20 seconds. Longer pauses result in a significant decrease in likelihood of a successful resuscitation. NOTE: The LUCAS device may be used in cases of Traumatic Cardiac arrest. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>neurogenic shock/treatment pathway/1</x:v>
+      </x:c>
+      <x:c r="H43" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I43" s="7" t="str"/>
+    </x:row>
+    <x:row r="44" ht="60" customHeight="1">
+      <x:c r="A44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S043</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/12#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consider ketamine if sedation is necessary during high quality CPR. NOTE: Placement and initiation of the device cannot exceed 20 seconds. Longer pauses result in a significant decrease in likelihood of a successful resuscitation. NOTE: The LUCAS device may be used in cases of Traumatic Cardiac arrest. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -12818,42 +12862,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>S044</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/2#6</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Select proper ET tube without stylet, test cuff and prepare suction.</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H44" s="7" t="str"/>
+      <x:c r="I44" s="7" t="str"/>
+    </x:row>
+    <x:row r="45" ht="60" customHeight="1">
+      <x:c r="A45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S044</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/2#6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select proper ET tube without stylet, test cuff and prepare suction.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -13369,42 +13415,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>S045</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/treatment-standing order/2#4</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>treatment-standing order</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>IV N.S.</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H45" s="7" t="str"/>
+      <x:c r="I45" s="7" t="str"/>
+    </x:row>
+    <x:row r="46" ht="60" customHeight="1">
+      <x:c r="A46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S045</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/treatment-standing order/2#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment-standing order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IV N.S.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -13920,42 +13968,46 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>S046</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>vascular access/reference/4#12</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Vascular Access</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Nausea, vomiting</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>[vascular access/treatment pathway/2]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>delirium with hyperagitation/treatment-standing order/2#4</x:v>
+      </x:c>
+      <x:c r="H46" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I46" s="7" t="str"/>
+    </x:row>
+    <x:row r="47" ht="60" customHeight="1">
+      <x:c r="A47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S046</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">vascular access/reference/4#12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Vascular Access</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nausea, vomiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[vascular access/treatment pathway/2]
 In the event that an IV cannot be established, and the IV is considered critical for the care of the patient, other peripheral sites may be used (i.e.: external jugular, feet, legs).
 [vascular access/treatment pathway/3]
 External jugular veins should never be the first line attempted unless the patient has no limbs for the initial attempts. INTs SHOULD NOT be used in external jugular access.
@@ -14410,42 +14462,46 @@
 [vascular access/reference/3#28]
 Treat for shock appropriate to the patient’s condition.
 [vascular access/reference/4#28]
-Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>S047</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>vascular access/reference/4#27</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Vascular Access</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Description of damage, estimated speed, airbag deployment as applicable</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>[vascular access/treatment pathway/2]
+Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
+        <x:v>vascular access/reference/4#12</x:v>
+      </x:c>
+      <x:c r="H47" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I47" s="7" t="str"/>
+    </x:row>
+    <x:row r="48" ht="60" customHeight="1">
+      <x:c r="A48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">vascular access/reference/4#27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Vascular Access</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Description of damage, estimated speed, airbag deployment as applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[vascular access/treatment pathway/2]
 In the event that an IV cannot be established, and the IV is considered critical for the care of the patient, other peripheral sites may be used (i.e.: external jugular, feet, legs).
 [vascular access/treatment pathway/3]
 External jugular veins should never be the first line attempted unless the patient has no limbs for the initial attempts. INTs SHOULD NOT be used in external jugular access.
@@ -14900,42 +14956,46 @@
 [vascular access/reference/3#28]
 Treat for shock appropriate to the patient’s condition.
 [vascular access/reference/4#28]
-Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>S048</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/7</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Obstetrical / Gynecological Complaints (Non-Delivery or Gynecological Only)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>EKG monitor PRN.</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>[obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/7]
+Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
+        <x:v>vascular access/reference/4#27</x:v>
+      </x:c>
+      <x:c r="H48" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I48" s="7" t="str"/>
+    </x:row>
+    <x:row r="49" ht="60" customHeight="1">
+      <x:c r="A49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S048</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Obstetrical / Gynecological Complaints (Non-Delivery or Gynecological Only)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EKG monitor PRN.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/7]
 EKG monitor PRN.
 [obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/6]
 INT or IV NS TKO unless signs of shock, then 20 cc/kg fluid bolus.
@@ -14948,42 +15008,46 @@
 [obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/4]
 Pulse oximetry.
 [obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/5]
-Glucose check.</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>S049</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/1.a.ii</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>If no, proceed with intubation, i-Gel Airway is acceptable</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Glucose check.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>obstetrical / gynecological complaints non-delivery or gynecological only/treatment pathway/7</x:v>
+      </x:c>
+      <x:c r="H49" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I49" s="7" t="str"/>
+    </x:row>
+    <x:row r="50" ht="60" customHeight="1">
+      <x:c r="A50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S049</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/1.a.ii</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If no, proceed with intubation, i-Gel Airway is acceptable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -15499,42 +15563,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>S050</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>post-intubation sedation/paramedic only/8</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Post-Intubation Sedation</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>paramedic only</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Remember that with children the intraosseous drug route is quick to establish and may be easier than gaining IV access.</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>[post-intubation sedation/paramedic only/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H50" s="7" t="str"/>
+      <x:c r="I50" s="7" t="str"/>
+    </x:row>
+    <x:row r="51" ht="60" customHeight="1">
+      <x:c r="A51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S050</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post-intubation sedation/paramedic only/8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post-Intubation Sedation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">paramedic only</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remember that with children the intraosseous drug route is quick to establish and may be easier than gaining IV access.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post-intubation sedation/paramedic only/1]
 An infant is less than one year of age.
 [post-intubation sedation/paramedic only/2]
 A child is from one to eight years of age.
@@ -15553,42 +15619,46 @@
 [post-intubation sedation/paramedic only/9]
 Children may be effectively ventilated using a BVM. This is the preferred method of ventilation in respiratory or cardiac arrest. EMT AEMT
 [post-intubation sedation/paramedic/-]
-1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>S051</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>seizures/treatment pathway/12</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Seizures</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>If narcotic overdose, Naloxone (Narcan) 0.4 mg IV/IO/IM/IN titrated to adequate ventilation (peds 0.1 mg/kg, titrated to adequate ventilation). If utilizing pre-filled delivery systems, dose per manufacturer’s instructions. May repeat dose. Synthetic opiates may require larger Naloxone doses. Physically manage the airway if no response after 8 mg Naloxone.</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>[seizures/treatment pathway/13]
+1 point Size Greater than 20 kg 10 – 20 kg Less than 10 kg Airway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="7" t="str">
+        <x:v>post-intubation sedation/paramedic only/8</x:v>
+      </x:c>
+      <x:c r="H51" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I51" s="7" t="str"/>
+    </x:row>
+    <x:row r="52" ht="60" customHeight="1">
+      <x:c r="A52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S051</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">seizures/treatment pathway/12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Seizures</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If narcotic overdose, Naloxone (Narcan) 0.4 mg IV/IO/IM/IN titrated to adequate ventilation (peds 0.1 mg/kg, titrated to adequate ventilation). If utilizing pre-filled delivery systems, dose per manufacturer’s instructions. May repeat dose. Synthetic opiates may require larger Naloxone doses. Physically manage the airway if no response after 8 mg Naloxone.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[seizures/treatment pathway/13]
 Adults – If actively seizing: Diazepam (Valium) SLOW IVP/IO 2-5 mg or Midazolam (Versed) 2-5 mg IV/IO/IM may repeat if seizure continues. LORazepam  1-2 mg IV, every 5 minutes or; 2-4 mg IM, every 10 minutes (maximum dose 8 mg). Consider Ketamine (if available) for refractory seizures unresponsive to benzodiazepines.
 [seizures/treatment pathway/9]
 IV NS TKO or INT.
@@ -15627,42 +15697,46 @@
 [seizures/paramedic stop/14.e]
 If seizure persists for 4 minutes repeat medication once.
 [seizures/paramedic stop/14.f]
-Additional Alternative: Diazepam rectal gel (DiaStat) is 0.2-0.5 mg/kg depending on age. See the dosing table for specific recommendations. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>S052</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/treatment-standing order/1#8</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>treatment-standing order</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>100% Oxygen and airway maintenance appropriate for pt. condition.</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Additional Alternative: Diazepam rectal gel (DiaStat) is 0.2-0.5 mg/kg depending on age. See the dosing table for specific recommendations. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" s="7" t="str">
+        <x:v>seizures/treatment pathway/12</x:v>
+      </x:c>
+      <x:c r="H52" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I52" s="7" t="str"/>
+    </x:row>
+    <x:row r="53" ht="60" customHeight="1">
+      <x:c r="A53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S052</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/treatment-standing order/1#8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment-standing order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">100% Oxygen and airway maintenance appropriate for pt. condition.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -16178,42 +16252,46 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>S053</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>eye trauma/treatment – standing order/4.c</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Eye Trauma</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>treatment – standing order</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>Consider covering unaffected eye</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>[eye trauma/treatment – standing order/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="7" t="str">
+        <x:v>delirium with hyperagitation/treatment-standing order/1#8</x:v>
+      </x:c>
+      <x:c r="H53" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I53" s="7" t="str"/>
+    </x:row>
+    <x:row r="54" ht="60" customHeight="1">
+      <x:c r="A54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S053</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">eye trauma/treatment – standing order/4.c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Eye Trauma</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment – standing order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consider covering unaffected eye</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[eye trauma/treatment – standing order/1]
 Oxygen and airway maintenance appropriate for the patient’s condition.
 [eye trauma/treatment – standing order/2]
 C-Spine protection PRN.
@@ -16250,42 +16328,46 @@
 [eye trauma/treatment – standing order/6.b.i]
 Apply cardiac monitor and assess for changes (EMT and above only)
 [eye trauma/treatment – standing order/6.b.ii]
-Apply vigorous pressure using heel of hand to affected eye for 3 – 5 seconds, then release (patient may perform this procedure and may be repeated as necessary EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>S054</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>unconscious / unresponsive / altered mental status/treatment pathway/1</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Unconscious / Unresponsive / Altered Mental Status</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Oxygen and airway maintenance appropriate to patient’s condition.</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>[unconscious / unresponsive / altered mental status/treatment pathway/10]
+Apply vigorous pressure using heel of hand to affected eye for 3 – 5 seconds, then release (patient may perform this procedure and may be repeated as necessary EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
+        <x:v>eye trauma/treatment – standing order/4.c</x:v>
+      </x:c>
+      <x:c r="H54" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I54" s="7" t="str"/>
+    </x:row>
+    <x:row r="55" ht="60" customHeight="1">
+      <x:c r="A55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S054</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">unconscious / unresponsive / altered mental status/treatment pathway/1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unconscious / Unresponsive / Altered Mental Status</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Oxygen and airway maintenance appropriate to patient’s condition.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[unconscious / unresponsive / altered mental status/treatment pathway/10]
 Contact Medical Control for further orders; 20 cc/kg NS fluid challenge (peds 20 cc/kg).
 [unconscious / unresponsive / altered mental status/treatment pathway/11]
 If hypoglycemic and unable to maintain airway, and CVA is not suspected, and the patient has a history of diabetes:
@@ -16312,42 +16394,46 @@
 [unconscious / unresponsive / altered mental status/treatment pathway/5]
 Glucose check.
 [unconscious / unresponsive / altered mental status/treatment pathway/6]
-Monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>S055</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/2#8</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Perform neuro exam to confirm meets criteria.</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" s="7" t="str">
+        <x:v>unconscious / unresponsive / altered mental status/treatment pathway/1</x:v>
+      </x:c>
+      <x:c r="H55" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I55" s="7" t="str"/>
+    </x:row>
+    <x:row r="56" ht="60" customHeight="1">
+      <x:c r="A56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S055</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/2#8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Perform neuro exam to confirm meets criteria.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -16863,42 +16949,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>S056</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>post resuscitation/notes/1#2</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Post Resuscitation</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Draw up 9 ml of normal saline into 10 ml syringe</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>[post resuscitation/notes/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H56" s="7" t="str"/>
+      <x:c r="I56" s="7" t="str"/>
+    </x:row>
+    <x:row r="57" ht="60" customHeight="1">
+      <x:c r="A57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S056</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post resuscitation/notes/1#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Draw up 9 ml of normal saline into 10 ml syringe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post resuscitation/notes/1]
 Oxygen and airway maintenance appropriate for patient’s condition.
 [post resuscitation/notes/2]
 Supportive care.
@@ -16935,42 +17023,46 @@
 [post resuscitation/emt stop here/12]
 Initiate Induced Hypothermia protocol if appropriate.
 [post resuscitation/emt stop here/13]
-Ensure Head of Bed elevated 30°.</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>S057</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>preamble/notes/16</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>&lt;preamble&gt;</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>The following refusal situations should be evaluated by a Paramedic if available:</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>[preamble/notes/1]
+Ensure Head of Bed elevated 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" s="7" t="str">
+        <x:v>post resuscitation/notes/1#2</x:v>
+      </x:c>
+      <x:c r="H57" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I57" s="7" t="str"/>
+    </x:row>
+    <x:row r="58" ht="60" customHeight="1">
+      <x:c r="A58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S057</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preamble/notes/16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">&lt;preamble&gt;</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The following refusal situations should be evaluated by a Paramedic if available:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[preamble/notes/1]
 The Emergency Medical Responder (EMR) will function under the current guidelines as stated in the AHA-BLS Healthcare Provider text. They shall also be responsible for other duties as assigned, within their scope of practice, as assigned by the AEMT or Paramedic.
 [preamble/notes/2]
 These Standing Orders and Protocols are in addition to the minimum guidelines for patient care as outlined in the DOT EMT Curriculum. The EMT and AEMT will assist ALS personnel as requested or as needed.
@@ -17163,42 +17255,46 @@
 [preamble/notes/3.f]
 Signs and symptoms of inadequate perfusion
 [preamble/notes/3.g]
-Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assisting other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. [Type here] Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director BLS/ALS State of Tennessee EMS Protocol Guidelines 2024-2025</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>S058</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>vascular access/reference/3#8</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Vascular Access</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Any obvious injuries or pain</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>[vascular access/treatment pathway/2]
+Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assisting other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. [Type here] Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director BLS/ALS State of Tennessee EMS Protocol Guidelines 2024-2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" s="7" t="str">
+        <x:v>preamble/notes/16</x:v>
+      </x:c>
+      <x:c r="H58" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I58" s="7" t="str"/>
+    </x:row>
+    <x:row r="59" ht="60" customHeight="1">
+      <x:c r="A59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S058</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">vascular access/reference/3#8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Vascular Access</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Any obvious injuries or pain</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[vascular access/treatment pathway/2]
 In the event that an IV cannot be established, and the IV is considered critical for the care of the patient, other peripheral sites may be used (i.e.: external jugular, feet, legs).
 [vascular access/treatment pathway/3]
 External jugular veins should never be the first line attempted unless the patient has no limbs for the initial attempts. INTs SHOULD NOT be used in external jugular access.
@@ -17653,42 +17749,46 @@
 [vascular access/reference/3#28]
 Treat for shock appropriate to the patient’s condition.
 [vascular access/reference/4#28]
-Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>S059</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>avulsed teeth/treatment pathway/2</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Avulsed Teeth</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>C-spine protection as appropriate.</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>[avulsed teeth/treatment pathway/6]
+Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
+        <x:v>vascular access/reference/3#8</x:v>
+      </x:c>
+      <x:c r="H59" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I59" s="7" t="str"/>
+    </x:row>
+    <x:row r="60" ht="60" customHeight="1">
+      <x:c r="A60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S059</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">avulsed teeth/treatment pathway/2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Avulsed Teeth</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">C-spine protection as appropriate.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[avulsed teeth/treatment pathway/6]
 Re-implantation is recommended at the scene as this creates maximum possibility of reattachment if possible. The following guidelines pertain to re-implantation at the scene:
 [avulsed teeth/treatment pathway/6.a]
 Applicable only for permanent teeth (i.e. with patients over 6.5 years of age)
@@ -17713,42 +17813,46 @@
 [avulsed teeth/treatment pathway/4]
 Pay attention to the airway, bleeding and avulsed teeth may cause airway obstruction.
 [avulsed teeth/treatment pathway/5]
-Supportive care. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>S060</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>neonatal resuscitation/treatment pathway/4.a.iii</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Neonatal Resuscitation</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Wrap and keep infant warm</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>[neonatal resuscitation/treatment pathway/8]
+Supportive care. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" s="7" t="str">
+        <x:v>avulsed teeth/treatment pathway/2</x:v>
+      </x:c>
+      <x:c r="H60" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I60" s="7" t="str"/>
+    </x:row>
+    <x:row r="61" ht="60" customHeight="1">
+      <x:c r="A61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S060</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">neonatal resuscitation/treatment pathway/4.a.iii</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Neonatal Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wrap and keep infant warm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F61" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[neonatal resuscitation/treatment pathway/8]
 INT or IV NS, if hypotensive bolus 20 cc/kg.
 [neonatal resuscitation/treatment pathway/9]
 If pulse rate is &gt; 60 keep warm, ventilate with BVM if necessary, transport.
@@ -17789,42 +17893,46 @@
 [neonatal resuscitation/treatment pathway/6]
 Pulse oximetry.
 [neonatal resuscitation/treatment pathway/7]
-Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>S061</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>chemical exposure/notes/4.c</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Chemical Exposure</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Transport and continue flushing if necessary and possible Liquid substance:</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>[chemical exposure/notes/1]
+Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" s="7" t="str">
+        <x:v>neonatal resuscitation/treatment pathway/4.a.iii</x:v>
+      </x:c>
+      <x:c r="H61" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I61" s="7" t="str"/>
+    </x:row>
+    <x:row r="62" ht="60" customHeight="1">
+      <x:c r="A62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S061</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">chemical exposure/notes/4.c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Chemical Exposure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Transport and continue flushing if necessary and possible Liquid substance:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F62" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[chemical exposure/notes/1]
 Oxygen and airway maintenance appropriate to the patient’s condition.
 [chemical exposure/notes/2]
 Supportive care.
@@ -17859,42 +17967,46 @@
 [chemical exposure/notes/4.a#6]
 Immediately flush eye with tap water or normal saline for 15 minutes
 [chemical exposure/notes/4.b#6]
-Contact Medical Control Note:  Coordinate through the HazMat officer prior to transport EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>S062</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>vascular access/reference/3#10</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Vascular Access</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Entrance / exit wounds if appropriate</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>[vascular access/treatment pathway/2]
+Contact Medical Control Note:  Coordinate through the HazMat officer prior to transport EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" s="7" t="str">
+        <x:v>chemical exposure/notes/4.c</x:v>
+      </x:c>
+      <x:c r="H62" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I62" s="7" t="str"/>
+    </x:row>
+    <x:row r="63" ht="60" customHeight="1">
+      <x:c r="A63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S062</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">vascular access/reference/3#10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Vascular Access</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Entrance / exit wounds if appropriate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[vascular access/treatment pathway/2]
 In the event that an IV cannot be established, and the IV is considered critical for the care of the patient, other peripheral sites may be used (i.e.: external jugular, feet, legs).
 [vascular access/treatment pathway/3]
 External jugular veins should never be the first line attempted unless the patient has no limbs for the initial attempts. INTs SHOULD NOT be used in external jugular access.
@@ -18349,42 +18461,46 @@
 [vascular access/reference/3#28]
 Treat for shock appropriate to the patient’s condition.
 [vascular access/reference/4#28]
-Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>S063</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>preamble/notes/3.g</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>&lt;preamble&gt;</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assist other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>[preamble/notes/1]
+Certain situations require rapid transport. Non-lifesaving procedures such as splinting and bandaging must not delay transport. Contact the responding emergency unit when any of the following exist: Airway obstructions that cannot be quickly relieved by mechanical methods such as suction or jaw-thrust maneuver. Traumatic cardiopulmonary arrest. Large open chest wound (sucking chest wound). Large flail chest. Tension pneumothorax. Major blunt chest trauma. Shock. Head injury with unconsciousness, unequal pupils, or decreasing level of consciousness. Tender abdomen. Unstable pelvis. Bilateral femur fractures. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" s="7" t="str">
+        <x:v>vascular access/reference/3#10</x:v>
+      </x:c>
+      <x:c r="H63" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I63" s="7" t="str"/>
+    </x:row>
+    <x:row r="64" ht="60" customHeight="1">
+      <x:c r="A64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S063</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preamble/notes/3.g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">&lt;preamble&gt;</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assist other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[preamble/notes/1]
 The Emergency Medical Responder (EMR) will function under the current guidelines as stated in the AHA-BLS Healthcare Provider text. They shall also be responsible for other duties as assigned, within their scope of practice, as assigned by the AEMT or Paramedic.
 [preamble/notes/2]
 These Standing Orders and Protocols are in addition to the minimum guidelines for patient care as outlined in the DOT EMT Curriculum. The EMT and AEMT will assist ALS personnel as requested or as needed.
@@ -18577,42 +18693,46 @@
 [preamble/notes/3.f]
 Signs and symptoms of inadequate perfusion
 [preamble/notes/3.g]
-Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assisting other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. [Type here] Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director BLS/ALS State of Tennessee EMS Protocol Guidelines 2024-2025</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>S064</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>ventricular tachycardia with a pulse/treatment pathway/8</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Ventricular Tachycardia with a Pulse</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>If rhythm possibly Torsades de Pointes – Go to Torsades de Pointes protocol.</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>[ventricular tachycardia with a pulse/treatment pathway/1]
+Altered level of consciousness Stable (asymptomatic): Indicates that the patient has no or very mild signs and symptoms associated with the current history of illness or trauma. Firefighter/Non-EMT: Personnel trained only in basic first aid and CPR. Responsible for immediately identifying and providing patient care and assisting other personnel upon their arrival and ensure continuity of patient care. Emergency Medical Responder (EMR): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to perform lifesaving interventions while awaiting additional EMS response. EMR may also assist higher level personnel at scene and during transport under medical direction and within scope of practice. Emergency Medical Technician (EMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic emergency care according to the standard of care and these Standing Orders and Protocols. Advanced Emergency Medical Technician (AEMT): Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide limited advanced emergency care according to the standard of care and these Standing Orders and Protocols. Paramedic: Personnel licensed by the Tennessee Department of Health, Office of EMS and authorized by the Medical Director to provide basic and advanced emergency patient care according to the Standard of Care and the EMS BLS and ALS Standing Orders and Protocols. Transfer of Care: Properly maintaining the continuity of care through appropriate verbal and/or written communication of patient care aspects to an equal or higher appropriate medical authority. Higher Medical Authority: Any medical personnel that possesses a current medical license or certificate recognized by the State of Tennessee with a higher level of medical training than the one possessed by Emergency Medical Services Personnel (MD, DO). Medical Control (transport): The instructions and advice provided by a physician, and the orders by a physician that define the treatment of the patient; to access Medical Control, contact the Emergency Department physician on duty of the patient’s first choice of destinations. If the patient does not have a preference, the patient’s condition and/or chief complaint may influence the choice of medical treatment facilities. All EMS Providers are expected to perform their duties in accordance with local, state, and federal guidelines. [Type here] Medical Director’s Statement I have taken great care to make certain that doses of medications and schedules of treatment are compatible with generally accepted standards at the time of publication. Much effort has gone into the development, production, and proof reading of these Standard Operating Procedures and Protocols. Unfortunately, this process may allow errors to go unnoticed or treatments may change between the creation of these protocols and their ultimate use. Please do not hesitate to contact me if you discover any errors, typos, dosage, or medication errors. I look forward to any questions, concerns, or comments regarding these protocols. I expect all EMS personnel to follow these guidelines, but also to utilize and exercise good judgment to provide the best care for all our patients. Joe Holley, MD FACEP FAEMS EMS Medical Director BLS/ALS State of Tennessee EMS Protocol Guidelines 2024-2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
+        <x:v>preamble/notes/3.g</x:v>
+      </x:c>
+      <x:c r="H64" s="7" t="str">
+        <x:v>reworded</x:v>
+      </x:c>
+      <x:c r="I64" s="7" t="str"/>
+    </x:row>
+    <x:row r="65" ht="60" customHeight="1">
+      <x:c r="A65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S064</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ventricular tachycardia with a pulse/treatment pathway/8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ventricular Tachycardia with a Pulse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If rhythm possibly Torsades de Pointes – Go to Torsades de Pointes protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[ventricular tachycardia with a pulse/treatment pathway/1]
 Oxygen and airway maintenance appropriate to the patient’s condition.
 [ventricular tachycardia with a pulse/treatment pathway/2]
 Supportive Care.
@@ -18645,42 +18765,46 @@
 [ventricular tachycardia with a pulse/treatment pathway/6]
 INT or IV NS TKO.
 [ventricular tachycardia with a pulse/treatment pathway/7]
-If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>S065</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>breech or limb presentation/treatment – standing order/7</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Breech or Limb Presentation</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>treatment – standing order</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>Position the mother in a supine position with head lowered and pelvis elevated. 8. Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>[breech or limb presentation/treatment pathway/10]
+If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" s="7" t="str">
+        <x:v>ventricular tachycardia with a pulse/treatment pathway/9</x:v>
+      </x:c>
+      <x:c r="H65" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I65" s="7" t="str"/>
+    </x:row>
+    <x:row r="66" ht="60" customHeight="1">
+      <x:c r="A66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S065</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">breech or limb presentation/treatment – standing order/7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Breech or Limb Presentation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment – standing order</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Position the mother in a supine position with head lowered and pelvis elevated. 8. Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[breech or limb presentation/treatment pathway/10]
 EKG monitor for arrythmias.
 [breech or limb presentation/treatment pathway/11]
 Transport ASAP.
@@ -18701,42 +18825,48 @@
 [breech or limb presentation/treatment – standing order/7]
 Position the mother in a supine position with head lowered and pelvis elevated.
 [breech or limb presentation/treatment – standing order/8]
-Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>S066</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>post resuscitation/notes/8</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Post Resuscitation</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Raise Head of Bed 30°.</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>[post resuscitation/notes/1]
+Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="7" t="str">
+        <x:v>breech or limb presentation/treatment – standing order/7</x:v>
+      </x:c>
+      <x:c r="H66" s="7" t="str">
+        <x:v>split</x:v>
+      </x:c>
+      <x:c r="I66" s="7" t="str">
+        <x:v>Only a narrower component of the older item is retained in this new item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="60" customHeight="1">
+      <x:c r="A67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S066</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post resuscitation/notes/8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Raise Head of Bed 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F67" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post resuscitation/notes/1]
 Oxygen and airway maintenance appropriate for patient’s condition.
 [post resuscitation/notes/2]
 Supportive care.
@@ -18773,42 +18903,46 @@
 [post resuscitation/emt stop here/12]
 Initiate Induced Hypothermia protocol if appropriate.
 [post resuscitation/emt stop here/13]
-Ensure Head of Bed elevated 30°.</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>S067</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/contraindications/2#4</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>contraindications</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Pain: Insertion of the IO device in conscious patients causes mild to moderate discomfort and is usually no more painful than a large bore IV. However, fluid infusion into the IO space is very painful and the following measures should be taken for conscious patients:</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Ensure Head of Bed elevated 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67" s="7" t="str">
+        <x:v>post resuscitation/notes/9</x:v>
+      </x:c>
+      <x:c r="H67" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I67" s="7" t="str"/>
+    </x:row>
+    <x:row r="68" ht="60" customHeight="1">
+      <x:c r="A68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S067</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/contraindications/2#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">contraindications</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pain: Insertion of the IO device in conscious patients causes mild to moderate discomfort and is usually no more painful than a large bore IV. However, fluid infusion into the IO space is very painful and the following measures should be taken for conscious patients:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F68" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -19324,42 +19458,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="7" t="inlineStr"/>
-      <c r="I68" s="7" t="inlineStr"/>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>S068</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/treatment and interventions/1.e</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>treatment and interventions</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Another severe or painful distracting injury is present f. Torticollis in children</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G68" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H68" s="7" t="str"/>
+      <x:c r="I68" s="7" t="str"/>
+    </x:row>
+    <x:row r="69" ht="60" customHeight="1">
+      <x:c r="A69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S068</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/treatment and interventions/1.e</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment and interventions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Another severe or painful distracting injury is present f. Torticollis in children</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F69" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -19624,42 +19760,48 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>S069</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/paramedic/2#3</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>paramedic</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>We have a XX year-old (&lt; 2 years, please give months) male/female s/p {brief mechanism explanation}. Broselow color is XXX.</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G69" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/treatment and interventions/1.e</x:v>
+      </x:c>
+      <x:c r="H69" s="7" t="str">
+        <x:v>split</x:v>
+      </x:c>
+      <x:c r="I69" s="7" t="str">
+        <x:v>Only a narrower component of the older item is retained in this new item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="60" customHeight="1">
+      <x:c r="A70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S069</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/paramedic/2#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">paramedic</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">We have a XX year-old (&lt; 2 years, please give months) male/female s/p {brief mechanism explanation}. Broselow color is XXX.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F70" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -20175,42 +20317,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>S070</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>drug ingestion/paramedic stop/d</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Drug Ingestion</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>paramedic stop</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>LORazepam (peds 0.1 mg/kg IV/IO, max single dose 4 mg, may repeat in 5 minutes if seizure activity continues; not to exceed 0.2 mg/kg total (maximum of 8 mg). If seizure persists for 4 minutes repeat medication once.  Contact Medical Control to consider Ketamine.</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>[drug ingestion/notes/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G70" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H70" s="7" t="str"/>
+      <x:c r="I70" s="7" t="str"/>
+    </x:row>
+    <x:row r="71" ht="60" customHeight="1">
+      <x:c r="A71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S070</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">drug ingestion/paramedic stop/d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Drug Ingestion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">paramedic stop</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LORazepam (peds 0.1 mg/kg IV/IO, max single dose 4 mg, may repeat in 5 minutes if seizure activity continues; not to exceed 0.2 mg/kg total (maximum of 8 mg). If seizure persists for 4 minutes repeat medication once.  Contact Medical Control to consider Ketamine.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F71" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[drug ingestion/notes/1]
 Oxygen and airway maintenance appropriate to patient’s condition.
 [drug ingestion/notes/2]
 Ensure personnel protection from toxin and/or unruly patient.
@@ -20241,42 +20385,46 @@
 [drug ingestion/paramedic stop/c]
 Midazolam (Versed) IN 0.3 mg/kg IN (max single dose 10 mg) with maximum total dose of 0.4 mg/kg.
 [drug ingestion/paramedic stop/d]
-LORazepam (peds 0.1 mg/kg IV/IO, max single dose 4 mg, may repeat in 5 minutes if seizure activity continues; not to exceed 0.2 mg/kg total (maximum of 8 mg). If seizure persists for 4 minutes repeat medication once.  Contact Medical Control to consider Ketamine. [Type here]</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr"/>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>S071</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/19</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>Continue holding the needle stabilizer in place and pull up the stylet (twisting may be necessary).</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+LORazepam (peds 0.1 mg/kg IV/IO, max single dose 4 mg, may repeat in 5 minutes if seizure activity continues; not to exceed 0.2 mg/kg total (maximum of 8 mg). If seizure persists for 4 minutes repeat medication once.  Contact Medical Control to consider Ketamine. [Type here]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G71" s="7" t="str">
+        <x:v>drug ingestion/paramedic stop/d</x:v>
+      </x:c>
+      <x:c r="H71" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I71" s="7" t="str"/>
+    </x:row>
+    <x:row r="72" ht="60" customHeight="1">
+      <x:c r="A72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S071</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/19</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Continue holding the needle stabilizer in place and pull up the stylet (twisting may be necessary).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F72" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -20792,42 +20940,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr"/>
-      <c r="I72" s="7" t="inlineStr"/>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>S072</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>trauma - penetrating/notes/5</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Trauma - Penetrating</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>Consider tourniquet use or hemorrhage control clamp. 6. Monitor, 12 lead EKG and transmission if applicable.</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>[trauma - penetrating/notes/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G72" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H72" s="7" t="str"/>
+      <x:c r="I72" s="7" t="str"/>
+    </x:row>
+    <x:row r="73" ht="60" customHeight="1">
+      <x:c r="A73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S072</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">trauma - penetrating/notes/5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Trauma - Penetrating</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consider tourniquet use or hemorrhage control clamp. 6. Monitor, 12 lead EKG and transmission if applicable.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F73" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[trauma - penetrating/notes/1]
 Initiate in-line C-Spine protection while simultaneously evaluating and controlling the patient’s ABCs. Incorporate the mechanism of injury into the patient care scheme.
 [trauma - penetrating/notes/2]
 Control any hemorrhage and simultaneously provide oxygen and airway maintenance appropriate to patient’s condition.
@@ -20850,42 +21000,48 @@
 [trauma - penetrating/aemt stop here/3]
 Label syringe Adult Push Dose Pressor IV Administration: Using above EPINEPHrine preparation (EPINEPHrine 10mcg/ml) 10 ml syringe, administer 5-10 mcg (0.5-1 ml) slow IV push (over 30-60 seconds) every 2-5 minutes as needed as a temporizing measure for severe hypotension. Note: Monitor HR and BP continuously while administering/titrating EPINEPHrine, as it may cause significant tachycardia and tachyarrhythmia in addition to the desired vasoconstriction
 [trauma - penetrating/aemt stop here/9]
-Contact Medical Control for pain management authorization.</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>S073</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>pre-eclampsia and eclampsia/treatment and interventions/4</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Pre-eclampsia and Eclampsia</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>treatment and interventions</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Apply cervical collar; patients who are unable to tolerate cervical collar may benefit from soft collars, pillows, or other padding. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>[pre-eclampsia and eclampsia/treatment pathway/6]
+Contact Medical Control for pain management authorization.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G73" s="7" t="str">
+        <x:v>trauma - penetrating/notes/5</x:v>
+      </x:c>
+      <x:c r="H73" s="7" t="str">
+        <x:v>split</x:v>
+      </x:c>
+      <x:c r="I73" s="7" t="str">
+        <x:v>The older row now appears divided between item 5 and item 6.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="60" customHeight="1">
+      <x:c r="A74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S073</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pre-eclampsia and eclampsia/treatment and interventions/4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pre-eclampsia and Eclampsia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment and interventions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Apply cervical collar; patients who are unable to tolerate cervical collar may benefit from soft collars, pillows, or other padding. BLS/ALS State of Tennessee Protocol Guidelines 2022-23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F74" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[pre-eclampsia and eclampsia/treatment pathway/6]
 EKG Monitor for arrythmias.
 [pre-eclampsia and eclampsia/treatment pathway/7]
 Diazepam (Valium) 5 mg slow IV or Midazolam (Versed) 2-5 mg IVP/IM per seizure protocol if generalized seizure activity.
@@ -21150,42 +21306,46 @@
 [pre-eclampsia and eclampsia/miscellaneous/6.a#2]
 State approved forms.
 [pre-eclampsia and eclampsia/miscellaneous/6.b#2]
-Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>S074</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>delirium with hyperagitation/procedure/1.e</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Delirium with HyperAgitation</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>procedure</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>Perform ACLS interventions as appropriate. f. Prepare for endotracheal intubation.</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>[delirium with hyperagitation/paramedic stop/4]
+Signed order in patient’s medical records: nursing home, hospice, or home care. Note: If DNR/POST form is used to withhold or terminate resuscitation efforts, a copy must be attached to the PCR. EMT AEMT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G74" s="7" t="str">
+        <x:v>pre-eclampsia and eclampsia/treatment and interventions/4</x:v>
+      </x:c>
+      <x:c r="H74" s="7" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="I74" s="7" t="str"/>
+    </x:row>
+    <x:row r="75" ht="60" customHeight="1">
+      <x:c r="A75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S074</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">delirium with hyperagitation/procedure/1.e</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delirium with HyperAgitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">procedure</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Perform ACLS interventions as appropriate. f. Prepare for endotracheal intubation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F75" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[delirium with hyperagitation/paramedic stop/4]
 Sedate the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg
 [delirium with hyperagitation/paramedic stop/5]
 Utilize Patient Restraint Medication Flow Chart as needed.
@@ -21701,42 +21861,44 @@
 Coma (Severe Exposure)
 [delirium with hyperagitation/gastrointestinal/1#16]
 Nausea
-[delirium wi</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>S075</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>sop 108 torsades de pointes/treatment pathway/8.a</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>SOP # 108 Torsades de Pointes</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>If &lt; 90 mmHg – unstable/symptomatic: i. Prepare for cardioversion at 50, then 100, then 200 joules, escalating as needed. (peds – 0.5-1 joule/kg in synchronized cardioversion). ii. Sedation as necessary. Diazepam (Valium) 2-5 mg IV (peds 0.1 mg/kg) OR Midazolam (Versed) 2-5 mg IV (peds 0.1 mg/kg) or Ketamine and/or Pain Medications per the pain management protocol. iii. Magnesium Sulfate 1 – 2 g IVP over 2 min</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>[sop 108 torsades de pointes/treatment pathway/1]
+[delirium wi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G75" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H75" s="7" t="str"/>
+      <x:c r="I75" s="7" t="str"/>
+    </x:row>
+    <x:row r="76" ht="60" customHeight="1">
+      <x:c r="A76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S075</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sop 108 torsades de pointes/treatment pathway/8.a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SOP # 108 Torsades de Pointes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If &lt; 90 mmHg – unstable/symptomatic: i. Prepare for cardioversion at 50, then 100, then 200 joules, escalating as needed. (peds – 0.5-1 joule/kg in synchronized cardioversion). ii. Sedation as necessary. Diazepam (Valium) 2-5 mg IV (peds 0.1 mg/kg) OR Midazolam (Versed) 2-5 mg IV (peds 0.1 mg/kg) or Ketamine and/or Pain Medications per the pain management protocol. iii. Magnesium Sulfate 1 – 2 g IVP over 2 min</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F76" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[sop 108 torsades de pointes/treatment pathway/1]
 Oxygen and airway maintenance appropriate for the patient’s condition.
 [sop 108 torsades de pointes/treatment pathway/2]
 Supportive care.
@@ -21759,42 +21921,46 @@
 [sop 108 torsades de pointes/treatment pathway/5#2]
 INT or IV NS TKO.
 [sop 108 torsades de pointes/treatment pathway/6]
-If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>S076</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>post resuscitation/notes/9.a</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Post Resuscitation</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>If anti-arrhythmic is administered:</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>[post resuscitation/notes/1]
+If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G76" s="7" t="str">
+        <x:v>sop 108 torsades de pointes/treatment pathway/7.a</x:v>
+      </x:c>
+      <x:c r="H76" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I76" s="7" t="str"/>
+    </x:row>
+    <x:row r="77" ht="60" customHeight="1">
+      <x:c r="A77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S076</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">post resuscitation/notes/9.a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Post Resuscitation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If anti-arrhythmic is administered:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F77" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[post resuscitation/notes/1]
 Oxygen and airway maintenance appropriate for patient’s condition.
 [post resuscitation/notes/2]
 Supportive care.
@@ -21831,42 +21997,46 @@
 [post resuscitation/emt stop here/12]
 Initiate Induced Hypothermia protocol if appropriate.
 [post resuscitation/emt stop here/13]
-Ensure Head of Bed elevated 30°.</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>S077</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>anaphylactic shock/treatment pathway/11</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Anaphylactic Shock</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Methylprednisolone (Solu-Medrol) 62.5 mg (if small in stature, sensitive to steroids, on chronic steroid therapy) or 125 mg IVP (peds contact Medical Control).</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>[anaphylactic shock/treatment pathway/1]
+Ensure Head of Bed elevated 30°.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G77" s="7" t="str">
+        <x:v>post resuscitation/notes/10.a</x:v>
+      </x:c>
+      <x:c r="H77" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I77" s="7" t="str"/>
+    </x:row>
+    <x:row r="78" ht="60" customHeight="1">
+      <x:c r="A78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S077</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">anaphylactic shock/treatment pathway/11</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Anaphylactic Shock</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Methylprednisolone (Solu-Medrol) 62.5 mg (if small in stature, sensitive to steroids, on chronic steroid therapy) or 125 mg IVP (peds contact Medical Control).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F78" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[anaphylactic shock/treatment pathway/1]
 Position of comfort, reassure.
 [anaphylactic shock/treatment pathway/2]
 Pulse oximetry, Oxygen and airway maintenance appropriate for patient’s condition.
@@ -21893,42 +22063,46 @@
 [anaphylactic shock/treatment pathway/11]
 DiphenhydrAMINE (Benadryl) 25-50 mg IV or deep IM (peds 1 mg/kg IVP).
 [anaphylactic shock/treatment pathway/12]
-Methylprednisolone (Solu-Medrol) 62.5 mg (if small in stature, sensitive to steroids, on chronic steroid therapy) or 125 mg IVP (peds contact Medical Control).</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>S078</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>ventricular tachycardia with a pulse/treatment pathway/10.b</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Ventricular Tachycardia with a Pulse</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>If rhythm converts, monitor for changes, transport.  If rhythm does not convert, administer Amiodarone 150 mg over 10 minutes (maximum 3 150 mg doses) (peds three doses of 5 mg/kg).</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>[ventricular tachycardia with a pulse/treatment pathway/1]
+Methylprednisolone (Solu-Medrol) 62.5 mg (if small in stature, sensitive to steroids, on chronic steroid therapy) or 125 mg IVP (peds contact Medical Control).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G78" s="7" t="str">
+        <x:v>anaphylactic shock/treatment pathway/12</x:v>
+      </x:c>
+      <x:c r="H78" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I78" s="7" t="str"/>
+    </x:row>
+    <x:row r="79" ht="60" customHeight="1">
+      <x:c r="A79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S078</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ventricular tachycardia with a pulse/treatment pathway/10.b</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ventricular Tachycardia with a Pulse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If rhythm converts, monitor for changes, transport.  If rhythm does not convert, administer Amiodarone 150 mg over 10 minutes (maximum 3 150 mg doses) (peds three doses of 5 mg/kg).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F79" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[ventricular tachycardia with a pulse/treatment pathway/1]
 Oxygen and airway maintenance appropriate to the patient’s condition.
 [ventricular tachycardia with a pulse/treatment pathway/2]
 Supportive Care.
@@ -21961,42 +22135,46 @@
 [ventricular tachycardia with a pulse/treatment pathway/6]
 INT or IV NS TKO.
 [ventricular tachycardia with a pulse/treatment pathway/7]
-If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>S079</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>tension pneumothorax/hypotension/9</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Tension Pneumothorax</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>hypotension</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>IV NS/LR TKO. If systolic BP &lt; 90 mmHg, IV NS/LR 20 cc/kg bolus (peds 20 cc/kg bolus). Target SBP is 90 – 110 mmHg in adult trauma patient.</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>[tension pneumothorax/hypotension/9]
+If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G79" s="7" t="str">
+        <x:v>ventricular tachycardia with a pulse/treatment pathway/11.b</x:v>
+      </x:c>
+      <x:c r="H79" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I79" s="7" t="str"/>
+    </x:row>
+    <x:row r="80" ht="60" customHeight="1">
+      <x:c r="A80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S079</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tension pneumothorax/hypotension/9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tension Pneumothorax</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypotension</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IV NS/LR TKO. If systolic BP &lt; 90 mmHg, IV NS/LR 20 cc/kg bolus (peds 20 cc/kg bolus). Target SBP is 90 – 110 mmHg in adult trauma patient.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F80" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[tension pneumothorax/hypotension/9]
 If tension pneumothorax suspected, perform needle decompression.  Use 14 g 3.5” needle (peds may use smaller 18 g needle).
 [tension pneumothorax/hypotension/8]
 IV NS/LR TKO. If systolic BP &lt; 90 mmHg, IV NS/LR 20 cc/kg bolus (peds 20 cc/kg bolus). Target SBP is 90 – 110 mmHg in adult trauma patient.
@@ -22013,42 +22191,46 @@
 [tension pneumothorax/hypotension/6]
 Pulse oximetry.
 [tension pneumothorax/hypotension/7]
-EKG monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr"/>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>S080</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>tension pneumothorax/hypotension/10</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Tension Pneumothorax</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>hypotension</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>If tension pneumothorax suspected, perform needle decompression.  Use 14 g 3.5” needle (peds may use smaller 18 g needle).</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>[tension pneumothorax/hypotension/9]
+EKG monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G80" s="7" t="str">
+        <x:v>tension pneumothorax/hypotension/8</x:v>
+      </x:c>
+      <x:c r="H80" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I80" s="7" t="str"/>
+    </x:row>
+    <x:row r="81" ht="60" customHeight="1">
+      <x:c r="A81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S080</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">tension pneumothorax/hypotension/10</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tension Pneumothorax</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypotension</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If tension pneumothorax suspected, perform needle decompression.  Use 14 g 3.5” needle (peds may use smaller 18 g needle).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F81" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[tension pneumothorax/hypotension/9]
 If tension pneumothorax suspected, perform needle decompression.  Use 14 g 3.5” needle (peds may use smaller 18 g needle).
 [tension pneumothorax/hypotension/8]
 IV NS/LR TKO. If systolic BP &lt; 90 mmHg, IV NS/LR 20 cc/kg bolus (peds 20 cc/kg bolus). Target SBP is 90 – 110 mmHg in adult trauma patient.
@@ -22065,42 +22247,46 @@
 [tension pneumothorax/hypotension/6]
 Pulse oximetry.
 [tension pneumothorax/hypotension/7]
-EKG monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>S081</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>ventricular tachycardia with a pulse/treatment pathway/10.a</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Ventricular Tachycardia with a Pulse</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>Have patient perform Valsalva Maneuver for 10 seconds and administer Amiodarone 150 mg (peds 5 mg/kg, may repeat up to a total of 15 mg/kg) over 10 minutes.</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>[ventricular tachycardia with a pulse/treatment pathway/1]
+EKG monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G81" s="7" t="str">
+        <x:v>tension pneumothorax/hypotension/9</x:v>
+      </x:c>
+      <x:c r="H81" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I81" s="7" t="str"/>
+    </x:row>
+    <x:row r="82" ht="60" customHeight="1">
+      <x:c r="A82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S081</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ventricular tachycardia with a pulse/treatment pathway/10.a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ventricular Tachycardia with a Pulse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Have patient perform Valsalva Maneuver for 10 seconds and administer Amiodarone 150 mg (peds 5 mg/kg, may repeat up to a total of 15 mg/kg) over 10 minutes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F82" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[ventricular tachycardia with a pulse/treatment pathway/1]
 Oxygen and airway maintenance appropriate to the patient’s condition.
 [ventricular tachycardia with a pulse/treatment pathway/2]
 Supportive Care.
@@ -22133,42 +22319,46 @@
 [ventricular tachycardia with a pulse/treatment pathway/6]
 INT or IV NS TKO.
 [ventricular tachycardia with a pulse/treatment pathway/7]
-If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr"/>
-      <c r="I82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>S082</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>medical complaint not specified under other protocols/treatment pathway/6#2</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>Medical Complaint Not Specified Under Other Protocols</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>[medical complaint not specified under other protocols/treatment pathway/1]
+If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G82" s="7" t="str">
+        <x:v>ventricular tachycardia with a pulse/treatment pathway/11.a</x:v>
+      </x:c>
+      <x:c r="H82" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I82" s="7" t="str"/>
+    </x:row>
+    <x:row r="83" ht="60" customHeight="1">
+      <x:c r="A83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S082</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">medical complaint not specified under other protocols/treatment pathway/6#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medical Complaint Not Specified Under Other Protocols</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F83" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[medical complaint not specified under other protocols/treatment pathway/1]
 Oxygen and airway maintenance appropriate for the patient’s condition.
 [medical complaint not specified under other protocols/treatment pathway/2]
 Patient positioning appropriate for condition.
@@ -22185,42 +22375,46 @@
 [medical complaint not specified under other protocols/treatment pathway/8]
 If indicated, Consider INT or IV NS TKO unless signs of shock, then 20 cc/kg fluid bolus.
 [medical complaint not specified under other protocols/treatment pathway/9]
-EKG monitor as indicated</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>S083</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>unconscious / unresponsive / altered mental status/treatment pathway/10.a</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Unconscious / Unresponsive / Altered Mental Status</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>If blood sugar is &lt; 80 mg/dL and symptomatic, infuse 250cc bag D10 until patient responds. (peds 2 mL/kg D25 IV/IO; IV Infusion of 10% Dextrose in 250mL for Hypoglycemia Max dose 250mL. Titrate to patient’s response/condition. Not to exceed 25g (1g/10ml))</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>[unconscious / unresponsive / altered mental status/treatment pathway/10]
+EKG monitor as indicated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G83" s="7" t="str">
+        <x:v>medical complaint not specified under other protocols/treatment pathway/7</x:v>
+      </x:c>
+      <x:c r="H83" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I83" s="7" t="str"/>
+    </x:row>
+    <x:row r="84" ht="60" customHeight="1">
+      <x:c r="A84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S083</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">unconscious / unresponsive / altered mental status/treatment pathway/10.a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unconscious / Unresponsive / Altered Mental Status</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">If blood sugar is &lt; 80 mg/dL and symptomatic, infuse 250cc bag D10 until patient responds. (peds 2 mL/kg D25 IV/IO; IV Infusion of 10% Dextrose in 250mL for Hypoglycemia Max dose 250mL. Titrate to patient’s response/condition. Not to exceed 25g (1g/10ml))</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F84" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[unconscious / unresponsive / altered mental status/treatment pathway/10]
 Contact Medical Control for further orders; 20 cc/kg NS fluid challenge (peds 20 cc/kg).
 [unconscious / unresponsive / altered mental status/treatment pathway/11]
 If hypoglycemic and unable to maintain airway, and CVA is not suspected, and the patient has a history of diabetes:
@@ -22247,42 +22441,46 @@
 [unconscious / unresponsive / altered mental status/treatment pathway/5]
 Glucose check.
 [unconscious / unresponsive / altered mental status/treatment pathway/6]
-Monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>S084</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>drowning/ near drowning/treatment pathway/7</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Drowning/ Near Drowning</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>INT or IV NS TKO, if hypotensive give 20 cc/kg bolus of fluid (peds 20 cc/kg).</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>[drowning/ near drowning/treatment pathway/8]
+Monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G84" s="7" t="str">
+        <x:v>unconscious / unresponsive / altered mental status/treatment pathway/11.a</x:v>
+      </x:c>
+      <x:c r="H84" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I84" s="7" t="str"/>
+    </x:row>
+    <x:row r="85" ht="60" customHeight="1">
+      <x:c r="A85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S084</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">drowning/ near drowning/treatment pathway/7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Drowning/ Near Drowning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">INT or IV NS TKO, if hypotensive give 20 cc/kg bolus of fluid (peds 20 cc/kg).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F85" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[drowning/ near drowning/treatment pathway/8]
 INT or IV NS TKO, if hypotensive give 20 cc/kg bolus of fluid (peds 20 cc/kg).
 [drowning/ near drowning/emt stop here/1]
 Oxygen and airway maintenance appropriate to the patient’s condition: Heimlich Maneuver may be indicated for airway obstruction Gastric decompression may be necessary to ensure adequate respirations or ventilations; if necessary, ventilations may be started prior to patient’s removal from the water
@@ -22299,42 +22497,46 @@
 [drowning/ near drowning/emt stop here/7]
 Monitor, 12 lead and transmission if applicable
 [drowning/ near drowning/emt stop here/9]
-EKG Monitor and treatment specific for arrhythmia.</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>S085</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>musculoskeletal trauma/treatment pathway/7#2</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Musculoskeletal Trauma</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>Monitor, 12 lead EKG and Transmission if applicable</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>[musculoskeletal trauma/treatment pathway/9]
+EKG Monitor and treatment specific for arrhythmia.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G85" s="7" t="str">
+        <x:v>drowning/ near drowning/treatment pathway/8</x:v>
+      </x:c>
+      <x:c r="H85" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I85" s="7" t="str"/>
+    </x:row>
+    <x:row r="86" ht="60" customHeight="1">
+      <x:c r="A86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S085</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">musculoskeletal trauma/treatment pathway/7#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Musculoskeletal Trauma</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Monitor, 12 lead EKG and Transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F86" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[musculoskeletal trauma/treatment pathway/9]
 Assess and manage Perfusion Status, Injuries, and Pain:
 [musculoskeletal trauma/treatment pathway/9.a]
 If systolic BP &gt; 90 mmHg or peds normal range for age
@@ -22367,42 +22569,46 @@
 [musculoskeletal trauma/treatment pathway/6]
 Pulse oximetry.
 [musculoskeletal trauma/treatment pathway/7]
-Monitor, 12 lead EKG and Transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr"/>
-    </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>S086</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>agitated or combative patient/notes/6#2</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Agitated or Combative Patient</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Sedation can be continued using Ketamine in the following dosages and routes of administration:</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>[agitated or combative patient/notes/5]
+Monitor, 12 lead EKG and Transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G86" s="7" t="str">
+        <x:v>musculoskeletal trauma/treatment pathway/7</x:v>
+      </x:c>
+      <x:c r="H86" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I86" s="7" t="str"/>
+    </x:row>
+    <x:row r="87" ht="60" customHeight="1">
+      <x:c r="A87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S086</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">agitated or combative patient/notes/6#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Agitated or Combative Patient</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sedation can be continued using Ketamine in the following dosages and routes of administration:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F87" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[agitated or combative patient/notes/5]
 If mental health crisis, consider contacting Mental Health Response.
 [agitated or combative patient/notes/6]
 Consider sedation of the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg.
@@ -22419,42 +22625,44 @@
 [agitated or combative patient/paramedic stop/3]
 Establish IV access with 0.9% NS.
 [agitated or combative patient/paramedic stop/4]
-Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>S087</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>unconscious / unresponsive / altered mental status/treatment pathway/9#2</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Unconscious / Unresponsive / Altered Mental Status</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>Administer Naloxone (Narcan) 0.4 mg IV/IM/IN/IO titrated to adequate ventilation (peds 0.1 mg/kg IV, max single dose 2 gm).  If utilizing pre-filled delivery systems, dose per manufacturer’s instructions. May repeat dose, with the exception of synthetic opioids which may require larger doses of Naloxone.  Physically manage the airway if no response after 8mg of Narcan.</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>[unconscious / unresponsive / altered mental status/treatment pathway/10]
+Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G87" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H87" s="7" t="str"/>
+      <x:c r="I87" s="7" t="str"/>
+    </x:row>
+    <x:row r="88" ht="60" customHeight="1">
+      <x:c r="A88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S087</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">unconscious / unresponsive / altered mental status/treatment pathway/9#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unconscious / Unresponsive / Altered Mental Status</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Administer Naloxone (Narcan) 0.4 mg IV/IM/IN/IO titrated to adequate ventilation (peds 0.1 mg/kg IV, max single dose 2 gm).  If utilizing pre-filled delivery systems, dose per manufacturer’s instructions. May repeat dose, with the exception of synthetic opioids which may require larger doses of Naloxone.  Physically manage the airway if no response after 8mg of Narcan.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F88" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[unconscious / unresponsive / altered mental status/treatment pathway/10]
 Contact Medical Control for further orders; 20 cc/kg NS fluid challenge (peds 20 cc/kg).
 [unconscious / unresponsive / altered mental status/treatment pathway/11]
 If hypoglycemic and unable to maintain airway, and CVA is not suspected, and the patient has a history of diabetes:
@@ -22481,42 +22689,48 @@
 [unconscious / unresponsive / altered mental status/treatment pathway/5]
 Glucose check.
 [unconscious / unresponsive / altered mental status/treatment pathway/6]
-Monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>S088</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>agitated or combative patient/notes/6.a</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Agitated or Combative Patient</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Ketamine 4 mg/kg IM</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>[agitated or combative patient/notes/5]
+Monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G88" s="7" t="str">
+        <x:v>unconscious / unresponsive / altered mental status/treatment pathway/9</x:v>
+      </x:c>
+      <x:c r="H88" s="7" t="str">
+        <x:v>substantive</x:v>
+      </x:c>
+      <x:c r="I88" s="7" t="str">
+        <x:v>Naloxone instruction is retained, but the pediatric max-dose unit changes from 2 gm to 2 mg.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="60" customHeight="1">
+      <x:c r="A89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S088</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">agitated or combative patient/notes/6.a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Agitated or Combative Patient</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ketamine 4 mg/kg IM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F89" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[agitated or combative patient/notes/5]
 If mental health crisis, consider contacting Mental Health Response.
 [agitated or combative patient/notes/6]
 Consider sedation of the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg.
@@ -22533,42 +22747,44 @@
 [agitated or combative patient/paramedic stop/3]
 Establish IV access with 0.9% NS.
 [agitated or combative patient/paramedic stop/4]
-Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>S089</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>sop 108 torsades de pointes/treatment pathway/9</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>SOP # 108 Torsades de Pointes</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>treatment pathway</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Transport.</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>[sop 108 torsades de pointes/treatment pathway/1]
+Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G89" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H89" s="7" t="str"/>
+      <x:c r="I89" s="7" t="str"/>
+    </x:row>
+    <x:row r="90" ht="60" customHeight="1">
+      <x:c r="A90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S089</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sop 108 torsades de pointes/treatment pathway/9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SOP # 108 Torsades de Pointes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">treatment pathway</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Transport.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F90" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[sop 108 torsades de pointes/treatment pathway/1]
 Oxygen and airway maintenance appropriate for the patient’s condition.
 [sop 108 torsades de pointes/treatment pathway/2]
 Supportive care.
@@ -22591,42 +22807,46 @@
 [sop 108 torsades de pointes/treatment pathway/5#2]
 INT or IV NS TKO.
 [sop 108 torsades de pointes/treatment pathway/6]
-If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
-      <c r="I90" s="7" t="inlineStr"/>
-    </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>S090</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>agitated or combative patient/notes/6.b</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Agitated or Combative Patient</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>Ketamine 2 mg/kg IV</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>[agitated or combative patient/notes/5]
+If glucose &lt;60, titrate D10 slowly per hypoglycemia guidelines.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G90" s="7" t="str">
+        <x:v>sop 108 torsades de pointes/treatment pathway/8</x:v>
+      </x:c>
+      <x:c r="H90" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I90" s="7" t="str"/>
+    </x:row>
+    <x:row r="91" ht="60" customHeight="1">
+      <x:c r="A91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S090</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">agitated or combative patient/notes/6.b</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Agitated or Combative Patient</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ketamine 2 mg/kg IV</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F91" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[agitated or combative patient/notes/5]
 If mental health crisis, consider contacting Mental Health Response.
 [agitated or combative patient/notes/6]
 Consider sedation of the patient as necessary by administering Versed via MAD 2-5 mg at a time up to 10 mg total or 0.1 mg/kg to a maximum of 10 mg.
@@ -22643,77 +22863,81 @@
 [agitated or combative patient/paramedic stop/3]
 Establish IV access with 0.9% NS.
 [agitated or combative patient/paramedic stop/4]
-Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>S091</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>behavioral health emergency/notes/9</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Behavioral Health Emergency</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>Medicate confused/combative patients as needed per Agitated Patient Protocol.</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>(no items found in this guideline in the new edition)</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
-    </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>S092</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>hyperglycemia associated with diabetes/hypotension/6#2</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Hyperglycemia Associated with Diabetes</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>hypotension</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>IV NS TKO or INT. If BS &gt;250 mg/dl, start 10-20cc/kg NS bolus if patient with signs of dehydration, vomiting, or DKA. (Peds 4 cc/kg/hr max 150cc/hr.  No Bolus).</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>[hyperglycemia associated with diabetes/hypotension/7]
+Monitor, 12 lead EKG and transmission if applicable. EMT, AEMT STOP HERE [Type here] BEHAVIORAL HEALTH EMERGENCIES SOP #702 Purpose: To establish criteria for EMS assessment, triage and treatment of patients with potential behavioral/mental health emergencies and direct transport to Behavioral Health. Definition: Behavioral health encompasses behavioral factors in chronic illness care, care of physical symptoms associated with stress rather than diseases, and health behaviors, as well as mental health and substance abuse conditions and diagnoses. Appropriate patients for protocol: Voluntary patient or patient on police or mental health hold. Primary 911 call or police request. Age between 18-70 years. Mental health complaint (depression, psychosis, suicide or homicidal ideation), substance abuse or behavioral disorder with no acute medical or traumatic condition requiring treatment. No evidence of trauma other than minor abrasions. Able to perform activities of daily living (ambulate, bathe, toileting, eat and drink) independently. If BG is obtained, between 60 and 300 mg/dl. Exclusion: Possible drug overdose or acute intoxication significantly impairing ability to ambulate or perform activities of daily living. Acute medical or traumatic condition including altered level of consciousness, chest or abdominal pain, significant bleeding, respiratory distress, or other acute illness or injury. Patients with abnormal physical findings or vital signs out of range: HR 60-130. O2 sat &gt; 90%. Systolic BP 90-200 mmHg. Diastolic BP &lt;110 mmHg. Temperature between 96.0 F and 100.4 F (38 C) if taken. Patients who require chemical restraint Signs/symptoms of acute drug/alcohol withdrawal (tachycardia, hypertension, tremor, visual hallucinations). Central or peripheral IV lines. Gastric or nasogastric tube feedings. Pregnancy greater than 20 weeks. Patients that require oxygen therapy. Patients requiring dialysis therapy. Any patient who demonstrates restlessness, agitation, confusion, or potentially violent behavior regardless of underlying diagnosis. Clinicians will assess the patient and take appropriate measures to sedate and restrain the patient prior to and during transport to ensure a safe and secure environment. BLS/ALS State of Tennessee Protocol Guidelines 2024-2025 SOP # 702 Behavioral Health Emergency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G91" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H91" s="7" t="str"/>
+      <x:c r="I91" s="7" t="str"/>
+    </x:row>
+    <x:row r="92" ht="60" customHeight="1">
+      <x:c r="A92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S091</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">behavioral health emergency/notes/9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Behavioral Health Emergency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">notes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Medicate confused/combative patients as needed per Agitated Patient Protocol.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F92" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">(no items found in this guideline in the new edition)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G92" s="7" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="H92" s="7" t="str"/>
+      <x:c r="I92" s="7" t="str"/>
+    </x:row>
+    <x:row r="93" ht="60" customHeight="1">
+      <x:c r="A93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">S092</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hyperglycemia associated with diabetes/hypotension/6#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hyperglycemia Associated with Diabetes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">hypotension</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IV NS TKO or INT. If BS &gt;250 mg/dl, start 10-20cc/kg NS bolus if patient with signs of dehydration, vomiting, or DKA. (Peds 4 cc/kg/hr max 150cc/hr.  No Bolus).</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F93" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[hyperglycemia associated with diabetes/hypotension/7]
 EKG Monitor Consider 12 lead EKG. Assess for Hyperkalemia, Ischemia.
 [hyperglycemia associated with diabetes/hypotension/6]
 IV NS TKO or INT. If BS &gt;250 mg/dl, start 10-20cc/kg NS bolus if patient with signs of dehydration, vomiting, or DKA. (Peds 4 cc/kg/hr max 150cc/hr.  No Bolus).
@@ -22726,20 +22950,23 @@
 [hyperglycemia associated with diabetes/hypotension/4]
 Glucose check.
 [hyperglycemia associated with diabetes/hypotension/5]
-Monitor, 12 lead EKG and transmission if applicable</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I93"/>
-  <dataValidations count="1">
-    <dataValidation sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Pick one from the list." type="list">
-      <formula1>"unchanged,reworded,substantive,merged,split,moved"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+Monitor, 12 lead EKG and transmission if applicable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G93" s="7" t="str">
+        <x:v>hyperglycemia associated with diabetes/hypotension/6</x:v>
+      </x:c>
+      <x:c r="H93" s="7" t="str">
+        <x:v>moved</x:v>
+      </x:c>
+      <x:c r="I93" s="7" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Invalid entry" error="Pick one from the list." sqref="H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93">
+      <x:formula1>"unchanged,reworded,substantive,merged,split,moved"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>